--- a/Fiche de mouvement _08-2026.xlsx
+++ b/Fiche de mouvement _08-2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lenovo\OneDrive\Documents\Samir\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{483393DB-B83A-4531-BFD0-30D03F11FF80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E25C636D-87C3-4CFC-B6A1-B6CFC1F1CDCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="14" xr2:uid="{BEED4A70-B61E-4C8D-BAB3-F17C8E5D544F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="11" xr2:uid="{BEED4A70-B61E-4C8D-BAB3-F17C8E5D544F}"/>
   </bookViews>
   <sheets>
     <sheet name="DASHBOARD" sheetId="1" r:id="rId1"/>
@@ -28,6 +28,8 @@
     <sheet name="17-08" sheetId="13" r:id="rId13"/>
     <sheet name="18-08" sheetId="14" r:id="rId14"/>
     <sheet name="19-08" sheetId="15" r:id="rId15"/>
+    <sheet name="20-08" sheetId="16" r:id="rId16"/>
+    <sheet name="23-08" sheetId="17" r:id="rId17"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -50,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="745" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="827" uniqueCount="291">
   <si>
     <t>Date</t>
   </si>
@@ -858,6 +860,72 @@
   </si>
   <si>
     <t>00335-510-31</t>
+  </si>
+  <si>
+    <t>TTNU102467 /0</t>
+  </si>
+  <si>
+    <t>00310-510-31</t>
+  </si>
+  <si>
+    <t>00053-511-31</t>
+  </si>
+  <si>
+    <t>00255-510-31</t>
+  </si>
+  <si>
+    <t>000310-510-31</t>
+  </si>
+  <si>
+    <t>3602841</t>
+  </si>
+  <si>
+    <t>CAIU818783 /6</t>
+  </si>
+  <si>
+    <t>CAIU819501 /9</t>
+  </si>
+  <si>
+    <t>CAXU959721 /0</t>
+  </si>
+  <si>
+    <t>CRSU928503 /0</t>
+  </si>
+  <si>
+    <t>HLD2681836</t>
+  </si>
+  <si>
+    <t>CXDU134311 /3</t>
+  </si>
+  <si>
+    <t>CXDU168050 /0</t>
+  </si>
+  <si>
+    <t>FCGU198565 /0</t>
+  </si>
+  <si>
+    <t>GESU661177 /9</t>
+  </si>
+  <si>
+    <t>HJMU133346 /2</t>
+  </si>
+  <si>
+    <t>HJMU152689 /9</t>
+  </si>
+  <si>
+    <t>SEGU466432 /6</t>
+  </si>
+  <si>
+    <t>TCNU646691 /7</t>
+  </si>
+  <si>
+    <t>TGHU694661 /0</t>
+  </si>
+  <si>
+    <t>GESU575475 /4</t>
+  </si>
+  <si>
+    <t>Depotage</t>
   </si>
 </sst>
 </file>
@@ -868,7 +936,7 @@
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="165" formatCode="##&quot;/&quot;##&quot;/&quot;####"/>
   </numFmts>
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -997,6 +1065,11 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="9">
@@ -1285,10 +1358,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1492,7 +1566,13 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="14" fontId="10" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="16" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1531,17 +1611,25 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="10" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{7CC03D9D-926F-4E09-97A5-FFE52C193664}"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="4">
+    <dxf>
+      <fill>
+        <patternFill>
+          <fgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1895,6 +1983,116 @@
         <a:xfrm>
           <a:off x="0" y="1"/>
           <a:ext cx="2000250" cy="457199"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing15.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>809625</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Image 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3E5187AF-A7A8-4CE9-953F-8B894BD86AA4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="1"/>
+          <a:ext cx="2000250" cy="514349"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing16.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>476250</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Image 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{03C0C295-E4CD-45AA-875F-065AA93D426B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="1"/>
+          <a:ext cx="2000250" cy="514349"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2975,17 +3173,39 @@
       <c r="F15" s="3"/>
     </row>
     <row r="16" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A16" s="2"/>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="4"/>
+      <c r="A16" s="2">
+        <v>46254</v>
+      </c>
+      <c r="B16" s="3">
+        <f>'20-08'!H1</f>
+        <v>0</v>
+      </c>
+      <c r="C16" s="3">
+        <f>'20-08'!H2</f>
+        <v>4</v>
+      </c>
+      <c r="D16" s="4">
+        <f t="shared" ref="D16:D17" si="7">SUM(B16:C16)</f>
+        <v>4</v>
+      </c>
       <c r="F16" s="3"/>
     </row>
     <row r="17" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A17" s="2"/>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="4"/>
+      <c r="A17" s="2">
+        <v>46257</v>
+      </c>
+      <c r="B17" s="3">
+        <f>'23-08'!H1</f>
+        <v>0</v>
+      </c>
+      <c r="C17" s="3">
+        <f>'23-08'!H2</f>
+        <v>0</v>
+      </c>
+      <c r="D17" s="4">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
       <c r="F17" s="3"/>
     </row>
     <row r="18" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -3040,11 +3260,11 @@
       </c>
       <c r="C24" s="6">
         <f>SUM(C2:C23)</f>
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D24" s="6">
         <f>SUM(D2:D23)</f>
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="E24" s="6"/>
       <c r="F24" s="6"/>
@@ -3101,16 +3321,16 @@
       </c>
     </row>
     <row r="3" spans="1:11" s="8" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="69" t="s">
+      <c r="A3" s="70" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="69"/>
-      <c r="C3" s="69"/>
-      <c r="D3" s="69"/>
-      <c r="E3" s="69"/>
-      <c r="F3" s="69"/>
-      <c r="G3" s="69"/>
-      <c r="H3" s="69"/>
+      <c r="B3" s="70"/>
+      <c r="C3" s="70"/>
+      <c r="D3" s="70"/>
+      <c r="E3" s="70"/>
+      <c r="F3" s="70"/>
+      <c r="G3" s="70"/>
+      <c r="H3" s="70"/>
     </row>
     <row r="4" spans="1:11" s="8" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="7"/>
@@ -3152,7 +3372,7 @@
       <c r="A8" s="42">
         <v>2</v>
       </c>
-      <c r="B8" s="80" t="s">
+      <c r="B8" s="82" t="s">
         <v>223</v>
       </c>
       <c r="C8" s="27">
@@ -3172,7 +3392,7 @@
       <c r="A9" s="41">
         <v>3</v>
       </c>
-      <c r="B9" s="81"/>
+      <c r="B9" s="83"/>
       <c r="C9" s="27">
         <v>46246</v>
       </c>
@@ -3608,16 +3828,16 @@
       </c>
     </row>
     <row r="3" spans="1:11" s="8" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="69" t="s">
+      <c r="A3" s="70" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="69"/>
-      <c r="C3" s="69"/>
-      <c r="D3" s="69"/>
-      <c r="E3" s="69"/>
-      <c r="F3" s="69"/>
-      <c r="G3" s="69"/>
-      <c r="H3" s="69"/>
+      <c r="B3" s="70"/>
+      <c r="C3" s="70"/>
+      <c r="D3" s="70"/>
+      <c r="E3" s="70"/>
+      <c r="F3" s="70"/>
+      <c r="G3" s="70"/>
+      <c r="H3" s="70"/>
     </row>
     <row r="4" spans="1:11" s="8" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="7"/>
@@ -4102,16 +4322,16 @@
       </c>
     </row>
     <row r="3" spans="1:11" s="8" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="69" t="s">
+      <c r="A3" s="70" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="69"/>
-      <c r="C3" s="69"/>
-      <c r="D3" s="69"/>
-      <c r="E3" s="69"/>
-      <c r="F3" s="69"/>
-      <c r="G3" s="69"/>
-      <c r="H3" s="69"/>
+      <c r="B3" s="70"/>
+      <c r="C3" s="70"/>
+      <c r="D3" s="70"/>
+      <c r="E3" s="70"/>
+      <c r="F3" s="70"/>
+      <c r="G3" s="70"/>
+      <c r="H3" s="70"/>
     </row>
     <row r="4" spans="1:11" s="8" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="7"/>
@@ -4665,16 +4885,16 @@
       </c>
     </row>
     <row r="3" spans="1:14" s="8" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="69" t="s">
+      <c r="A3" s="70" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="69"/>
-      <c r="C3" s="69"/>
-      <c r="D3" s="69"/>
-      <c r="E3" s="69"/>
-      <c r="F3" s="69"/>
-      <c r="G3" s="69"/>
-      <c r="H3" s="69"/>
+      <c r="B3" s="70"/>
+      <c r="C3" s="70"/>
+      <c r="D3" s="70"/>
+      <c r="E3" s="70"/>
+      <c r="F3" s="70"/>
+      <c r="G3" s="70"/>
+      <c r="H3" s="70"/>
     </row>
     <row r="4" spans="1:14" s="8" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="7"/>
@@ -5149,16 +5369,16 @@
       </c>
     </row>
     <row r="3" spans="1:11" s="8" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="69" t="s">
+      <c r="A3" s="70" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="69"/>
-      <c r="C3" s="69"/>
-      <c r="D3" s="69"/>
-      <c r="E3" s="69"/>
-      <c r="F3" s="69"/>
-      <c r="G3" s="69"/>
-      <c r="H3" s="69"/>
+      <c r="B3" s="70"/>
+      <c r="C3" s="70"/>
+      <c r="D3" s="70"/>
+      <c r="E3" s="70"/>
+      <c r="F3" s="70"/>
+      <c r="G3" s="70"/>
+      <c r="H3" s="70"/>
     </row>
     <row r="4" spans="1:11" s="8" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="7"/>
@@ -5703,16 +5923,16 @@
       </c>
     </row>
     <row r="3" spans="1:11" s="8" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="69" t="s">
+      <c r="A3" s="70" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="69"/>
-      <c r="C3" s="69"/>
-      <c r="D3" s="69"/>
-      <c r="E3" s="69"/>
-      <c r="F3" s="69"/>
-      <c r="G3" s="69"/>
-      <c r="H3" s="69"/>
+      <c r="B3" s="70"/>
+      <c r="C3" s="70"/>
+      <c r="D3" s="70"/>
+      <c r="E3" s="70"/>
+      <c r="F3" s="70"/>
+      <c r="G3" s="70"/>
+      <c r="H3" s="70"/>
     </row>
     <row r="4" spans="1:11" s="8" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="7"/>
@@ -5754,7 +5974,7 @@
       <c r="A8" s="42">
         <v>2</v>
       </c>
-      <c r="B8" s="82" t="s">
+      <c r="B8" s="71" t="s">
         <v>257</v>
       </c>
       <c r="C8" s="27">
@@ -5774,7 +5994,7 @@
       <c r="A9" s="41">
         <v>3</v>
       </c>
-      <c r="B9" s="82"/>
+      <c r="B9" s="71"/>
       <c r="C9" s="27">
         <v>46253</v>
       </c>
@@ -6281,7 +6501,7 @@
       <c r="A38" s="36">
         <v>6</v>
       </c>
-      <c r="B38" s="83"/>
+      <c r="B38" s="69"/>
       <c r="C38" s="50"/>
       <c r="D38" s="50"/>
       <c r="E38" s="38"/>
@@ -6314,6 +6534,1282 @@
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F8:F14 F36:F39 F19" xr:uid="{7BC0F096-037C-46D4-82EE-AA4D89FADB78}">
+      <formula1>"20,40,45,50"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4F06B22-942E-4FE6-B0CD-F6BABABBED57}">
+  <dimension ref="A1:S40"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3.140625" style="24" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.7109375" style="24" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" style="24" customWidth="1"/>
+    <col min="4" max="4" width="19.140625" style="24" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="24" customWidth="1"/>
+    <col min="6" max="6" width="14" style="24" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.140625" style="24" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="11.42578125" style="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" s="8" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="7"/>
+      <c r="H1" s="9">
+        <f>COUNTIF(C8:C14,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" s="8" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="7"/>
+      <c r="F2" s="9">
+        <f>COUNTIFS(B19:B22,"&lt;&gt;",C19:C22,"VH")</f>
+        <v>0</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="9">
+        <f>COUNTA(C19:C28)-F2</f>
+        <v>4</v>
+      </c>
+      <c r="I2" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="J2" s="11">
+        <f>COUNTIF(H19:H24,"VIDE")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" s="8" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="70" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="70"/>
+      <c r="C3" s="70"/>
+      <c r="D3" s="70"/>
+      <c r="E3" s="70"/>
+      <c r="F3" s="70"/>
+      <c r="G3" s="70"/>
+      <c r="H3" s="70"/>
+    </row>
+    <row r="4" spans="1:11" s="8" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="7"/>
+    </row>
+    <row r="5" spans="1:11" s="8" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="7"/>
+      <c r="B5" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="13">
+        <v>46253</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" s="8" customFormat="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="7"/>
+      <c r="B6" s="14"/>
+    </row>
+    <row r="7" spans="1:11" s="8" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A7" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="17" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" s="8" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A8" s="42">
+        <v>2</v>
+      </c>
+      <c r="B8" s="71"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="44"/>
+      <c r="E8" s="44"/>
+      <c r="F8" s="50"/>
+    </row>
+    <row r="9" spans="1:11" s="8" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A9" s="41">
+        <v>3</v>
+      </c>
+      <c r="B9" s="71"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="50"/>
+      <c r="E9" s="50"/>
+      <c r="F9" s="50"/>
+    </row>
+    <row r="10" spans="1:11" s="8" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A10" s="42">
+        <v>4</v>
+      </c>
+      <c r="B10" s="51"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="50"/>
+      <c r="E10" s="50"/>
+      <c r="F10" s="50"/>
+    </row>
+    <row r="11" spans="1:11" s="8" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A11" s="42">
+        <v>5</v>
+      </c>
+      <c r="B11" s="51"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="50"/>
+      <c r="E11" s="50"/>
+      <c r="F11" s="50"/>
+    </row>
+    <row r="12" spans="1:11" s="8" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A12" s="41">
+        <v>6</v>
+      </c>
+      <c r="B12" s="51"/>
+      <c r="C12" s="27"/>
+      <c r="D12" s="50"/>
+      <c r="E12" s="50"/>
+      <c r="F12" s="50"/>
+      <c r="K12" s="8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" s="8" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A13" s="41">
+        <v>7</v>
+      </c>
+      <c r="B13" s="51"/>
+      <c r="C13" s="27"/>
+      <c r="D13" s="44"/>
+      <c r="E13" s="44"/>
+      <c r="F13" s="41"/>
+    </row>
+    <row r="14" spans="1:11" s="8" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A14" s="42">
+        <v>8</v>
+      </c>
+      <c r="B14" s="41"/>
+      <c r="C14" s="27"/>
+      <c r="D14" s="44"/>
+      <c r="E14" s="44"/>
+      <c r="F14" s="41"/>
+    </row>
+    <row r="15" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="7"/>
+      <c r="B15" s="25"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="25"/>
+    </row>
+    <row r="16" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="7"/>
+      <c r="B16" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="G16" s="25"/>
+    </row>
+    <row r="17" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="7"/>
+      <c r="B17" s="14"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="8"/>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A18" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="B18" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="D18" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="E18" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="F18" s="17" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="36">
+        <v>1</v>
+      </c>
+      <c r="B19" s="69">
+        <v>46254</v>
+      </c>
+      <c r="C19" s="38" t="s">
+        <v>273</v>
+      </c>
+      <c r="D19" s="41" t="s">
+        <v>197</v>
+      </c>
+      <c r="E19" s="50">
+        <v>3959</v>
+      </c>
+      <c r="F19" s="50">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="36">
+        <v>2</v>
+      </c>
+      <c r="B20" s="69">
+        <v>46254</v>
+      </c>
+      <c r="C20" s="38" t="s">
+        <v>270</v>
+      </c>
+      <c r="D20" s="44" t="s">
+        <v>131</v>
+      </c>
+      <c r="E20" s="44" t="s">
+        <v>132</v>
+      </c>
+      <c r="F20" s="50">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="36">
+        <v>3</v>
+      </c>
+      <c r="B21" s="69">
+        <v>46254</v>
+      </c>
+      <c r="C21" s="38" t="s">
+        <v>271</v>
+      </c>
+      <c r="D21" s="44" t="s">
+        <v>133</v>
+      </c>
+      <c r="E21" s="44" t="s">
+        <v>134</v>
+      </c>
+      <c r="F21" s="50">
+        <v>40</v>
+      </c>
+      <c r="G21" s="24" t="s">
+        <v>42</v>
+      </c>
+      <c r="J21" s="67"/>
+      <c r="K21" s="67"/>
+      <c r="L21" s="67"/>
+      <c r="M21" s="67"/>
+      <c r="N21" s="67"/>
+    </row>
+    <row r="22" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="36">
+        <v>4</v>
+      </c>
+      <c r="B22" s="69">
+        <v>46254</v>
+      </c>
+      <c r="C22" s="38" t="s">
+        <v>272</v>
+      </c>
+      <c r="D22" s="44" t="s">
+        <v>135</v>
+      </c>
+      <c r="E22" s="44" t="s">
+        <v>136</v>
+      </c>
+      <c r="F22" s="50">
+        <v>40</v>
+      </c>
+      <c r="J22" s="67"/>
+      <c r="K22" s="68"/>
+      <c r="L22" s="67"/>
+      <c r="M22" s="67"/>
+      <c r="N22" s="67"/>
+    </row>
+    <row r="23" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="36">
+        <v>5</v>
+      </c>
+      <c r="B23" s="69"/>
+      <c r="C23" s="38"/>
+      <c r="D23" s="50"/>
+      <c r="E23" s="38"/>
+      <c r="F23" s="38"/>
+    </row>
+    <row r="24" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="36">
+        <v>6</v>
+      </c>
+      <c r="B24" s="27"/>
+      <c r="C24" s="38"/>
+      <c r="D24" s="50"/>
+      <c r="E24" s="41"/>
+      <c r="F24" s="29"/>
+      <c r="M24" s="67"/>
+      <c r="O24" s="67"/>
+      <c r="P24" s="67"/>
+      <c r="Q24"/>
+      <c r="R24"/>
+      <c r="S24"/>
+    </row>
+    <row r="25" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="36">
+        <v>7</v>
+      </c>
+      <c r="B25" s="27"/>
+      <c r="C25" s="38"/>
+      <c r="D25" s="43"/>
+      <c r="E25" s="50"/>
+      <c r="F25" s="29"/>
+      <c r="M25" s="67"/>
+      <c r="N25" s="68"/>
+      <c r="O25" s="67"/>
+      <c r="P25" s="67"/>
+      <c r="R25" s="67"/>
+      <c r="S25" s="67"/>
+    </row>
+    <row r="26" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="36">
+        <v>8</v>
+      </c>
+      <c r="B26" s="27"/>
+      <c r="C26" s="28"/>
+      <c r="D26" s="39"/>
+      <c r="E26" s="29"/>
+      <c r="F26" s="29"/>
+      <c r="L26" s="67"/>
+      <c r="M26" s="68"/>
+      <c r="N26" s="67"/>
+      <c r="O26" s="67"/>
+      <c r="Q26"/>
+      <c r="R26"/>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A27" s="36">
+        <v>9</v>
+      </c>
+      <c r="B27" s="27"/>
+      <c r="C27" s="41"/>
+      <c r="D27" s="44"/>
+      <c r="E27" s="41"/>
+      <c r="F27" s="29"/>
+    </row>
+    <row r="28" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A28" s="36">
+        <v>10</v>
+      </c>
+      <c r="B28" s="27"/>
+      <c r="C28" s="41"/>
+      <c r="D28" s="44"/>
+      <c r="E28" s="41"/>
+      <c r="F28" s="29"/>
+      <c r="G28" s="25"/>
+    </row>
+    <row r="29" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A29" s="7"/>
+      <c r="B29" s="12"/>
+      <c r="C29" s="8"/>
+      <c r="D29" s="45"/>
+      <c r="E29" s="8"/>
+      <c r="F29" s="8"/>
+      <c r="G29" s="25"/>
+    </row>
+    <row r="30" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A30" s="7"/>
+      <c r="B30" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C30" s="8"/>
+      <c r="D30" s="45"/>
+      <c r="E30" s="8"/>
+      <c r="F30" s="8"/>
+      <c r="G30" s="25"/>
+    </row>
+    <row r="31" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="7"/>
+      <c r="B31" s="14"/>
+      <c r="C31" s="8"/>
+      <c r="D31" s="8"/>
+      <c r="E31" s="8"/>
+      <c r="F31" s="8"/>
+      <c r="G31" s="8"/>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A32" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="B32" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="C32" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="D32" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="E32" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="F32" s="17" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="41">
+        <v>1</v>
+      </c>
+      <c r="B33" s="27">
+        <v>46253</v>
+      </c>
+      <c r="C33" s="39" t="s">
+        <v>269</v>
+      </c>
+      <c r="D33" s="64" t="s">
+        <v>274</v>
+      </c>
+      <c r="E33" s="38">
+        <v>3504</v>
+      </c>
+      <c r="F33" s="28">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="41">
+        <v>2</v>
+      </c>
+      <c r="B34" s="27"/>
+      <c r="C34" s="39"/>
+      <c r="D34" s="28"/>
+      <c r="E34" s="38"/>
+      <c r="F34" s="28"/>
+    </row>
+    <row r="35" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="41">
+        <v>3</v>
+      </c>
+      <c r="B35" s="27"/>
+      <c r="C35" s="44"/>
+      <c r="D35" s="39"/>
+      <c r="E35" s="28"/>
+      <c r="F35" s="38"/>
+    </row>
+    <row r="36" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="41">
+        <v>4</v>
+      </c>
+      <c r="B36" s="27"/>
+      <c r="C36" s="44"/>
+      <c r="D36" s="39"/>
+      <c r="E36" s="28"/>
+      <c r="F36" s="50"/>
+    </row>
+    <row r="37" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="36">
+        <v>5</v>
+      </c>
+      <c r="B37" s="27"/>
+      <c r="C37" s="50"/>
+      <c r="D37" s="39"/>
+      <c r="E37" s="28"/>
+      <c r="F37" s="50"/>
+    </row>
+    <row r="38" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="36">
+        <v>6</v>
+      </c>
+      <c r="B38" s="69"/>
+      <c r="C38" s="50"/>
+      <c r="D38" s="50"/>
+      <c r="E38" s="38"/>
+      <c r="F38" s="50"/>
+    </row>
+    <row r="39" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="36">
+        <v>7</v>
+      </c>
+      <c r="B39" s="27"/>
+      <c r="C39" s="59"/>
+      <c r="D39" s="59"/>
+      <c r="E39" s="41"/>
+      <c r="F39" s="59"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="36">
+        <v>8</v>
+      </c>
+      <c r="B40" s="27"/>
+      <c r="C40" s="44"/>
+      <c r="D40" s="44"/>
+      <c r="E40" s="40"/>
+      <c r="F40" s="40"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="B8:B9"/>
+  </mergeCells>
+  <phoneticPr fontId="13" type="noConversion"/>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F8:F14 F36:F39 F19:F22" xr:uid="{B3C966D0-8377-48F4-BC74-CB6D2549356E}">
+      <formula1>"20,40,45,50"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66CED9A8-3757-4456-8DC3-1F82E70D5470}">
+  <dimension ref="A1:J46"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3.140625" style="24" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.7109375" style="24" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" style="24" customWidth="1"/>
+    <col min="4" max="4" width="19.140625" style="24" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="24" customWidth="1"/>
+    <col min="6" max="6" width="14" style="24" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.140625" style="24" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="11.42578125" style="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="7"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="9">
+        <f>COUNTIF(C8:C14,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" s="8"/>
+    </row>
+    <row r="2" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="7"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="9">
+        <f>COUNTIFS(B19:B22,"&lt;&gt;",C19:C22,"VH")</f>
+        <v>0</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="9">
+        <f>COUNTA(C19:C28)-F2</f>
+        <v>0</v>
+      </c>
+      <c r="I2" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="J2" s="11">
+        <f>COUNTIF(H19:H24,"VIDE")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="70" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="70"/>
+      <c r="C3" s="70"/>
+      <c r="D3" s="70"/>
+      <c r="E3" s="70"/>
+      <c r="F3" s="70"/>
+      <c r="G3" s="70"/>
+      <c r="H3" s="70"/>
+      <c r="I3" s="8"/>
+      <c r="J3" s="8"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="7"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="8"/>
+    </row>
+    <row r="5" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="7"/>
+      <c r="B5" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="13">
+        <v>46253</v>
+      </c>
+      <c r="H5" s="8"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="8"/>
+    </row>
+    <row r="6" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="7"/>
+      <c r="B6" s="14"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8"/>
+      <c r="J6" s="8"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="42">
+        <v>2</v>
+      </c>
+      <c r="B8" s="71"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="44"/>
+      <c r="E8" s="44"/>
+      <c r="F8" s="50"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="41">
+        <v>3</v>
+      </c>
+      <c r="B9" s="71"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="50"/>
+      <c r="E9" s="50"/>
+      <c r="F9" s="50"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="8"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="42">
+        <v>4</v>
+      </c>
+      <c r="B10" s="51"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="50"/>
+      <c r="E10" s="50"/>
+      <c r="F10" s="50"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="42">
+        <v>5</v>
+      </c>
+      <c r="B11" s="51"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="50"/>
+      <c r="E11" s="50"/>
+      <c r="F11" s="50"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="41">
+        <v>6</v>
+      </c>
+      <c r="B12" s="51"/>
+      <c r="C12" s="27"/>
+      <c r="D12" s="50"/>
+      <c r="E12" s="50"/>
+      <c r="F12" s="50"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="41">
+        <v>7</v>
+      </c>
+      <c r="B13" s="51"/>
+      <c r="C13" s="27"/>
+      <c r="D13" s="44"/>
+      <c r="E13" s="44"/>
+      <c r="F13" s="41"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="8"/>
+      <c r="J13" s="8"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="42">
+        <v>8</v>
+      </c>
+      <c r="B14" s="41"/>
+      <c r="C14" s="27"/>
+      <c r="D14" s="44"/>
+      <c r="E14" s="44"/>
+      <c r="F14" s="41"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="8"/>
+    </row>
+    <row r="15" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="7"/>
+      <c r="B15" s="25"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="25"/>
+    </row>
+    <row r="16" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="7"/>
+      <c r="B16" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="G16" s="25"/>
+    </row>
+    <row r="17" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="7"/>
+      <c r="B17" s="14"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="8"/>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="B18" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="D18" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="E18" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="F18" s="17" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" s="36">
+        <v>1</v>
+      </c>
+      <c r="B19" s="69">
+        <v>46254</v>
+      </c>
+      <c r="C19" s="47"/>
+      <c r="D19" s="41"/>
+      <c r="E19" s="50"/>
+      <c r="F19" s="50"/>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" s="36">
+        <v>2</v>
+      </c>
+      <c r="B20" s="69">
+        <v>46254</v>
+      </c>
+      <c r="C20" s="38"/>
+      <c r="D20" s="44"/>
+      <c r="E20" s="44"/>
+      <c r="F20" s="50"/>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" s="36">
+        <v>3</v>
+      </c>
+      <c r="B21" s="69">
+        <v>46254</v>
+      </c>
+      <c r="C21" s="38"/>
+      <c r="D21" s="44"/>
+      <c r="E21" s="44"/>
+      <c r="F21" s="50"/>
+      <c r="G21" s="24" t="s">
+        <v>42</v>
+      </c>
+      <c r="J21" s="67"/>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" s="36">
+        <v>4</v>
+      </c>
+      <c r="B22" s="69">
+        <v>46254</v>
+      </c>
+      <c r="C22" s="38"/>
+      <c r="D22" s="44"/>
+      <c r="E22" s="44"/>
+      <c r="F22" s="50"/>
+      <c r="J22" s="67"/>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" s="36">
+        <v>5</v>
+      </c>
+      <c r="B23" s="69"/>
+      <c r="C23" s="38"/>
+      <c r="D23" s="50"/>
+      <c r="E23" s="38"/>
+      <c r="F23" s="38"/>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" s="36">
+        <v>6</v>
+      </c>
+      <c r="B24" s="27"/>
+      <c r="C24" s="38"/>
+      <c r="D24" s="50"/>
+      <c r="E24" s="41"/>
+      <c r="F24" s="29"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" s="36">
+        <v>7</v>
+      </c>
+      <c r="B25" s="27"/>
+      <c r="C25" s="38"/>
+      <c r="D25" s="43"/>
+      <c r="E25" s="50"/>
+      <c r="F25" s="29"/>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" s="36">
+        <v>8</v>
+      </c>
+      <c r="B26" s="27"/>
+      <c r="C26" s="28"/>
+      <c r="D26" s="39"/>
+      <c r="E26" s="29"/>
+      <c r="F26" s="29"/>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" s="36">
+        <v>9</v>
+      </c>
+      <c r="B27" s="27"/>
+      <c r="C27" s="41"/>
+      <c r="D27" s="44"/>
+      <c r="E27" s="41"/>
+      <c r="F27" s="29"/>
+    </row>
+    <row r="28" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A28" s="36">
+        <v>10</v>
+      </c>
+      <c r="B28" s="27"/>
+      <c r="C28" s="41"/>
+      <c r="D28" s="44"/>
+      <c r="E28" s="41"/>
+      <c r="F28" s="29"/>
+      <c r="G28" s="25"/>
+    </row>
+    <row r="29" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A29" s="7"/>
+      <c r="B29" s="12"/>
+      <c r="C29" s="8"/>
+      <c r="D29" s="45"/>
+      <c r="E29" s="8"/>
+      <c r="F29" s="8"/>
+      <c r="G29" s="25"/>
+    </row>
+    <row r="30" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A30" s="7"/>
+      <c r="B30" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C30" s="8"/>
+      <c r="D30" s="45"/>
+      <c r="E30" s="8"/>
+      <c r="F30" s="8"/>
+      <c r="G30" s="25"/>
+    </row>
+    <row r="31" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="7"/>
+      <c r="B31" s="14"/>
+      <c r="C31" s="8"/>
+      <c r="D31" s="8"/>
+      <c r="E31" s="8"/>
+      <c r="F31" s="8"/>
+      <c r="G31" s="8"/>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="B32" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="C32" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="D32" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="E32" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="F32" s="17" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="41">
+        <v>1</v>
+      </c>
+      <c r="B33" s="27">
+        <v>46257</v>
+      </c>
+      <c r="C33" s="84" t="s">
+        <v>275</v>
+      </c>
+      <c r="D33" s="44">
+        <v>403430</v>
+      </c>
+      <c r="E33" s="38">
+        <v>3561</v>
+      </c>
+      <c r="F33" s="28">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="41">
+        <v>2</v>
+      </c>
+      <c r="B34" s="27">
+        <v>46257</v>
+      </c>
+      <c r="C34" s="84" t="s">
+        <v>276</v>
+      </c>
+      <c r="D34" s="44">
+        <v>403420</v>
+      </c>
+      <c r="E34" s="38">
+        <v>3562</v>
+      </c>
+      <c r="F34" s="28">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="41">
+        <v>3</v>
+      </c>
+      <c r="B35" s="27">
+        <v>46257</v>
+      </c>
+      <c r="C35" s="44" t="s">
+        <v>277</v>
+      </c>
+      <c r="D35" s="44">
+        <v>207502</v>
+      </c>
+      <c r="E35" s="38">
+        <v>3564</v>
+      </c>
+      <c r="F35" s="28">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="41">
+        <v>4</v>
+      </c>
+      <c r="B36" s="27">
+        <v>46257</v>
+      </c>
+      <c r="C36" s="44" t="s">
+        <v>278</v>
+      </c>
+      <c r="D36" s="44" t="s">
+        <v>279</v>
+      </c>
+      <c r="E36" s="38">
+        <v>3563</v>
+      </c>
+      <c r="F36" s="28">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="41">
+        <v>5</v>
+      </c>
+      <c r="B37" s="27">
+        <v>46257</v>
+      </c>
+      <c r="C37" s="44" t="s">
+        <v>280</v>
+      </c>
+      <c r="D37" s="44">
+        <v>482341</v>
+      </c>
+      <c r="E37" s="38">
+        <v>3565</v>
+      </c>
+      <c r="F37" s="28">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="41">
+        <v>6</v>
+      </c>
+      <c r="B38" s="27">
+        <v>46257</v>
+      </c>
+      <c r="C38" s="44" t="s">
+        <v>281</v>
+      </c>
+      <c r="D38" s="44">
+        <v>482345</v>
+      </c>
+      <c r="E38" s="38">
+        <v>3566</v>
+      </c>
+      <c r="F38" s="28">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="41">
+        <v>7</v>
+      </c>
+      <c r="B39" s="27">
+        <v>46257</v>
+      </c>
+      <c r="C39" s="44" t="s">
+        <v>282</v>
+      </c>
+      <c r="D39" s="44">
+        <v>403418</v>
+      </c>
+      <c r="E39" s="38">
+        <v>3567</v>
+      </c>
+      <c r="F39" s="28">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="41">
+        <v>8</v>
+      </c>
+      <c r="B40" s="27">
+        <v>46257</v>
+      </c>
+      <c r="C40" s="44" t="s">
+        <v>289</v>
+      </c>
+      <c r="D40" s="44"/>
+      <c r="E40" s="38">
+        <v>3568</v>
+      </c>
+      <c r="F40" s="28">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="41">
+        <v>9</v>
+      </c>
+      <c r="B41" s="27">
+        <v>46257</v>
+      </c>
+      <c r="C41" s="44" t="s">
+        <v>283</v>
+      </c>
+      <c r="D41" s="44">
+        <v>534715</v>
+      </c>
+      <c r="E41" s="38">
+        <v>3569</v>
+      </c>
+      <c r="F41" s="28">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="41">
+        <v>10</v>
+      </c>
+      <c r="B42" s="27">
+        <v>46257</v>
+      </c>
+      <c r="C42" s="44" t="s">
+        <v>284</v>
+      </c>
+      <c r="D42" s="44">
+        <v>482343</v>
+      </c>
+      <c r="E42" s="38">
+        <v>3570</v>
+      </c>
+      <c r="F42" s="28">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="41">
+        <v>11</v>
+      </c>
+      <c r="B43" s="27">
+        <v>46257</v>
+      </c>
+      <c r="C43" s="44" t="s">
+        <v>285</v>
+      </c>
+      <c r="D43" s="44">
+        <v>403415</v>
+      </c>
+      <c r="E43" s="38">
+        <v>3503</v>
+      </c>
+      <c r="F43" s="28">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="41">
+        <v>12</v>
+      </c>
+      <c r="B44" s="27">
+        <v>46257</v>
+      </c>
+      <c r="C44" s="44" t="s">
+        <v>286</v>
+      </c>
+      <c r="D44" s="44">
+        <v>403425</v>
+      </c>
+      <c r="E44" s="38">
+        <v>3502</v>
+      </c>
+      <c r="F44" s="28">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="41">
+        <v>13</v>
+      </c>
+      <c r="B45" s="27">
+        <v>46257</v>
+      </c>
+      <c r="C45" s="44" t="s">
+        <v>287</v>
+      </c>
+      <c r="D45" s="44">
+        <v>482350</v>
+      </c>
+      <c r="E45" s="38">
+        <v>3501</v>
+      </c>
+      <c r="F45" s="28">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="41">
+        <v>14</v>
+      </c>
+      <c r="B46" s="27">
+        <v>46257</v>
+      </c>
+      <c r="C46" s="44" t="s">
+        <v>288</v>
+      </c>
+      <c r="D46" s="44">
+        <v>2681587</v>
+      </c>
+      <c r="E46" s="38">
+        <v>3580</v>
+      </c>
+      <c r="F46" s="28">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="B8:B9"/>
+  </mergeCells>
+  <phoneticPr fontId="13" type="noConversion"/>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F8:F14 F19:F22" xr:uid="{2017016A-DB0F-4C7A-A34F-906C9B5FB086}">
       <formula1>"20,40,45,50"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -6370,16 +7866,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="8" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="69" t="s">
+      <c r="A3" s="70" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="69"/>
-      <c r="C3" s="69"/>
-      <c r="D3" s="69"/>
-      <c r="E3" s="69"/>
-      <c r="F3" s="69"/>
-      <c r="G3" s="69"/>
-      <c r="H3" s="69"/>
+      <c r="B3" s="70"/>
+      <c r="C3" s="70"/>
+      <c r="D3" s="70"/>
+      <c r="E3" s="70"/>
+      <c r="F3" s="70"/>
+      <c r="G3" s="70"/>
+      <c r="H3" s="70"/>
     </row>
     <row r="4" spans="1:10" s="8" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="7"/>
@@ -6872,7 +8368,7 @@
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
   <conditionalFormatting sqref="G10">
-    <cfRule type="expression" dxfId="2" priority="1">
+    <cfRule type="expression" dxfId="3" priority="1">
       <formula>LEFT(CELL("format",C10))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6929,16 +8425,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="8" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="69" t="s">
+      <c r="A3" s="70" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="69"/>
-      <c r="C3" s="69"/>
-      <c r="D3" s="69"/>
-      <c r="E3" s="69"/>
-      <c r="F3" s="69"/>
-      <c r="G3" s="69"/>
-      <c r="H3" s="69"/>
+      <c r="B3" s="70"/>
+      <c r="C3" s="70"/>
+      <c r="D3" s="70"/>
+      <c r="E3" s="70"/>
+      <c r="F3" s="70"/>
+      <c r="G3" s="70"/>
+      <c r="H3" s="70"/>
     </row>
     <row r="4" spans="1:10" s="8" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="7"/>
@@ -7479,7 +8975,7 @@
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
   <conditionalFormatting sqref="G10">
-    <cfRule type="expression" dxfId="1" priority="1">
+    <cfRule type="expression" dxfId="2" priority="1">
       <formula>LEFT(CELL("format",C10))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7541,16 +9037,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="8" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="69" t="s">
+      <c r="A3" s="70" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="69"/>
-      <c r="C3" s="69"/>
-      <c r="D3" s="69"/>
-      <c r="E3" s="69"/>
-      <c r="F3" s="69"/>
-      <c r="G3" s="69"/>
-      <c r="H3" s="69"/>
+      <c r="B3" s="70"/>
+      <c r="C3" s="70"/>
+      <c r="D3" s="70"/>
+      <c r="E3" s="70"/>
+      <c r="F3" s="70"/>
+      <c r="G3" s="70"/>
+      <c r="H3" s="70"/>
     </row>
     <row r="4" spans="1:10" s="8" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="7"/>
@@ -7954,7 +9450,7 @@
     <mergeCell ref="A3:H3"/>
   </mergeCells>
   <conditionalFormatting sqref="G10">
-    <cfRule type="expression" dxfId="0" priority="1">
+    <cfRule type="expression" dxfId="1" priority="1">
       <formula>LEFT(CELL("format",C10))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8020,16 +9516,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="8" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="69" t="s">
+      <c r="A3" s="70" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="69"/>
-      <c r="C3" s="69"/>
-      <c r="D3" s="69"/>
-      <c r="E3" s="69"/>
-      <c r="F3" s="69"/>
-      <c r="G3" s="69"/>
-      <c r="H3" s="69"/>
+      <c r="B3" s="70"/>
+      <c r="C3" s="70"/>
+      <c r="D3" s="70"/>
+      <c r="E3" s="70"/>
+      <c r="F3" s="70"/>
+      <c r="G3" s="70"/>
+      <c r="H3" s="70"/>
     </row>
     <row r="4" spans="1:10" s="8" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="7"/>
@@ -8091,7 +9587,7 @@
       <c r="A9" s="42">
         <v>2</v>
       </c>
-      <c r="B9" s="70" t="s">
+      <c r="B9" s="72" t="s">
         <v>142</v>
       </c>
       <c r="C9" s="51">
@@ -8111,7 +9607,7 @@
       <c r="A10" s="36">
         <v>3</v>
       </c>
-      <c r="B10" s="71"/>
+      <c r="B10" s="73"/>
       <c r="C10" s="51">
         <v>46239</v>
       </c>
@@ -8129,7 +9625,7 @@
       <c r="A11" s="42">
         <v>4</v>
       </c>
-      <c r="B11" s="71"/>
+      <c r="B11" s="73"/>
       <c r="C11" s="51">
         <v>46239</v>
       </c>
@@ -8147,7 +9643,7 @@
       <c r="A12" s="42">
         <v>5</v>
       </c>
-      <c r="B12" s="71"/>
+      <c r="B12" s="73"/>
       <c r="C12" s="51">
         <v>46239</v>
       </c>
@@ -8165,7 +9661,7 @@
       <c r="A13" s="36">
         <v>6</v>
       </c>
-      <c r="B13" s="71"/>
+      <c r="B13" s="73"/>
       <c r="C13" s="51"/>
       <c r="D13" s="54"/>
       <c r="E13" s="53"/>
@@ -8175,7 +9671,7 @@
       <c r="A14" s="42">
         <v>7</v>
       </c>
-      <c r="B14" s="71"/>
+      <c r="B14" s="73"/>
       <c r="C14" s="51">
         <v>46239</v>
       </c>
@@ -8193,7 +9689,7 @@
       <c r="A15" s="42">
         <v>8</v>
       </c>
-      <c r="B15" s="72"/>
+      <c r="B15" s="74"/>
       <c r="C15" s="51">
         <v>46239</v>
       </c>
@@ -8211,7 +9707,7 @@
       <c r="A16" s="36">
         <v>9</v>
       </c>
-      <c r="B16" s="70" t="s">
+      <c r="B16" s="72" t="s">
         <v>143</v>
       </c>
       <c r="C16" s="51">
@@ -8231,7 +9727,7 @@
       <c r="A17" s="42">
         <v>10</v>
       </c>
-      <c r="B17" s="72"/>
+      <c r="B17" s="74"/>
       <c r="C17" s="51">
         <v>46239</v>
       </c>
@@ -8249,10 +9745,10 @@
       <c r="A18" s="42">
         <v>16</v>
       </c>
-      <c r="B18" s="70" t="s">
+      <c r="B18" s="72" t="s">
         <v>145</v>
       </c>
-      <c r="C18" s="75"/>
+      <c r="C18" s="77"/>
       <c r="D18" s="52" t="s">
         <v>117</v>
       </c>
@@ -8262,7 +9758,7 @@
       <c r="F18" s="54" t="s">
         <v>95</v>
       </c>
-      <c r="G18" s="77" t="s">
+      <c r="G18" s="79" t="s">
         <v>154</v>
       </c>
     </row>
@@ -8270,8 +9766,8 @@
       <c r="A19" s="42">
         <v>17</v>
       </c>
-      <c r="B19" s="72"/>
-      <c r="C19" s="76"/>
+      <c r="B19" s="74"/>
+      <c r="C19" s="78"/>
       <c r="D19" s="52" t="s">
         <v>119</v>
       </c>
@@ -8281,13 +9777,13 @@
       <c r="F19" s="54" t="s">
         <v>95</v>
       </c>
-      <c r="G19" s="77"/>
+      <c r="G19" s="79"/>
     </row>
     <row r="20" spans="1:7" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="36">
         <v>18</v>
       </c>
-      <c r="B20" s="70" t="s">
+      <c r="B20" s="72" t="s">
         <v>146</v>
       </c>
       <c r="C20" s="51">
@@ -8307,7 +9803,7 @@
       <c r="A21" s="42">
         <v>19</v>
       </c>
-      <c r="B21" s="72"/>
+      <c r="B21" s="74"/>
       <c r="C21" s="51">
         <v>46239</v>
       </c>
@@ -8325,7 +9821,7 @@
       <c r="A22" s="42">
         <v>20</v>
       </c>
-      <c r="B22" s="70" t="s">
+      <c r="B22" s="72" t="s">
         <v>147</v>
       </c>
       <c r="C22" s="51">
@@ -8345,7 +9841,7 @@
       <c r="A23" s="36">
         <v>21</v>
       </c>
-      <c r="B23" s="71"/>
+      <c r="B23" s="73"/>
       <c r="C23" s="51"/>
       <c r="D23" s="52" t="s">
         <v>127</v>
@@ -8361,7 +9857,7 @@
       <c r="A24" s="42">
         <v>22</v>
       </c>
-      <c r="B24" s="72"/>
+      <c r="B24" s="74"/>
       <c r="C24" s="51">
         <v>46239</v>
       </c>
@@ -8379,7 +9875,7 @@
       <c r="A25" s="42">
         <v>23</v>
       </c>
-      <c r="B25" s="73" t="s">
+      <c r="B25" s="75" t="s">
         <v>148</v>
       </c>
       <c r="C25" s="51"/>
@@ -8397,7 +9893,7 @@
       <c r="A26" s="36">
         <v>24</v>
       </c>
-      <c r="B26" s="73"/>
+      <c r="B26" s="75"/>
       <c r="C26" s="51">
         <v>46239</v>
       </c>
@@ -8415,7 +9911,7 @@
       <c r="A27" s="42">
         <v>25</v>
       </c>
-      <c r="B27" s="74"/>
+      <c r="B27" s="76"/>
       <c r="C27" s="51">
         <v>46239</v>
       </c>
@@ -8433,7 +9929,7 @@
       <c r="A28" s="42">
         <v>26</v>
       </c>
-      <c r="B28" s="73" t="s">
+      <c r="B28" s="75" t="s">
         <v>149</v>
       </c>
       <c r="C28" s="51">
@@ -8453,7 +9949,7 @@
       <c r="A29" s="36">
         <v>27</v>
       </c>
-      <c r="B29" s="74"/>
+      <c r="B29" s="76"/>
       <c r="C29" s="51">
         <v>46239</v>
       </c>
@@ -8716,16 +10212,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="8" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="69" t="s">
+      <c r="A3" s="70" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="69"/>
-      <c r="C3" s="69"/>
-      <c r="D3" s="69"/>
-      <c r="E3" s="69"/>
-      <c r="F3" s="69"/>
-      <c r="G3" s="69"/>
-      <c r="H3" s="69"/>
+      <c r="B3" s="70"/>
+      <c r="C3" s="70"/>
+      <c r="D3" s="70"/>
+      <c r="E3" s="70"/>
+      <c r="F3" s="70"/>
+      <c r="G3" s="70"/>
+      <c r="H3" s="70"/>
     </row>
     <row r="4" spans="1:10" s="8" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="7"/>
@@ -8787,7 +10283,7 @@
       <c r="A9" s="42">
         <v>2</v>
       </c>
-      <c r="B9" s="75" t="s">
+      <c r="B9" s="77" t="s">
         <v>144</v>
       </c>
       <c r="C9" s="27">
@@ -8807,7 +10303,7 @@
       <c r="A10" s="36">
         <v>3</v>
       </c>
-      <c r="B10" s="78"/>
+      <c r="B10" s="80"/>
       <c r="C10" s="27">
         <v>46240</v>
       </c>
@@ -8825,7 +10321,7 @@
       <c r="A11" s="42">
         <v>4</v>
       </c>
-      <c r="B11" s="78"/>
+      <c r="B11" s="80"/>
       <c r="C11" s="27"/>
       <c r="D11" s="41" t="s">
         <v>112</v>
@@ -8841,7 +10337,7 @@
       <c r="A12" s="42">
         <v>5</v>
       </c>
-      <c r="B12" s="78"/>
+      <c r="B12" s="80"/>
       <c r="C12" s="27"/>
       <c r="D12" s="41" t="s">
         <v>114</v>
@@ -8857,7 +10353,7 @@
       <c r="A13" s="36">
         <v>6</v>
       </c>
-      <c r="B13" s="76"/>
+      <c r="B13" s="78"/>
       <c r="C13" s="27">
         <v>46240</v>
       </c>
@@ -9394,16 +10890,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="8" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="69" t="s">
+      <c r="A3" s="70" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="69"/>
-      <c r="C3" s="69"/>
-      <c r="D3" s="69"/>
-      <c r="E3" s="69"/>
-      <c r="F3" s="69"/>
-      <c r="G3" s="69"/>
-      <c r="H3" s="69"/>
+      <c r="B3" s="70"/>
+      <c r="C3" s="70"/>
+      <c r="D3" s="70"/>
+      <c r="E3" s="70"/>
+      <c r="F3" s="70"/>
+      <c r="G3" s="70"/>
+      <c r="H3" s="70"/>
     </row>
     <row r="4" spans="1:10" s="8" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="7"/>
@@ -9445,7 +10941,7 @@
       <c r="A8" s="36">
         <v>1</v>
       </c>
-      <c r="B8" s="75" t="s">
+      <c r="B8" s="77" t="s">
         <v>144</v>
       </c>
       <c r="C8" s="27">
@@ -9465,7 +10961,7 @@
       <c r="A9" s="42">
         <v>2</v>
       </c>
-      <c r="B9" s="76"/>
+      <c r="B9" s="78"/>
       <c r="C9" s="27">
         <v>46243</v>
       </c>
@@ -9907,16 +11403,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="8" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="69" t="s">
+      <c r="A3" s="70" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="69"/>
-      <c r="C3" s="69"/>
-      <c r="D3" s="69"/>
-      <c r="E3" s="69"/>
-      <c r="F3" s="69"/>
-      <c r="G3" s="69"/>
-      <c r="H3" s="69"/>
+      <c r="B3" s="70"/>
+      <c r="C3" s="70"/>
+      <c r="D3" s="70"/>
+      <c r="E3" s="70"/>
+      <c r="F3" s="70"/>
+      <c r="G3" s="70"/>
+      <c r="H3" s="70"/>
     </row>
     <row r="4" spans="1:10" s="8" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="7"/>
@@ -9958,7 +11454,7 @@
       <c r="A8" s="36">
         <v>1</v>
       </c>
-      <c r="B8" s="79" t="s">
+      <c r="B8" s="81" t="s">
         <v>194</v>
       </c>
       <c r="C8" s="27">
@@ -9978,7 +11474,7 @@
       <c r="A9" s="42">
         <v>2</v>
       </c>
-      <c r="B9" s="79"/>
+      <c r="B9" s="81"/>
       <c r="C9" s="27"/>
       <c r="D9" s="29">
         <v>3517</v>
@@ -9994,7 +11490,7 @@
       <c r="A10" s="36">
         <v>3</v>
       </c>
-      <c r="B10" s="79"/>
+      <c r="B10" s="81"/>
       <c r="C10" s="27">
         <v>46244</v>
       </c>
@@ -10012,7 +11508,7 @@
       <c r="A11" s="42">
         <v>4</v>
       </c>
-      <c r="B11" s="79"/>
+      <c r="B11" s="81"/>
       <c r="C11" s="27">
         <v>46244</v>
       </c>
@@ -10650,16 +12146,16 @@
       </c>
     </row>
     <row r="3" spans="1:11" s="8" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="69" t="s">
+      <c r="A3" s="70" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="69"/>
-      <c r="C3" s="69"/>
-      <c r="D3" s="69"/>
-      <c r="E3" s="69"/>
-      <c r="F3" s="69"/>
-      <c r="G3" s="69"/>
-      <c r="H3" s="69"/>
+      <c r="B3" s="70"/>
+      <c r="C3" s="70"/>
+      <c r="D3" s="70"/>
+      <c r="E3" s="70"/>
+      <c r="F3" s="70"/>
+      <c r="G3" s="70"/>
+      <c r="H3" s="70"/>
     </row>
     <row r="4" spans="1:11" s="8" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="7"/>
@@ -10696,6 +12192,9 @@
       <c r="F7" s="17" t="s">
         <v>15</v>
       </c>
+      <c r="G7" s="17" t="s">
+        <v>290</v>
+      </c>
     </row>
     <row r="8" spans="1:11" s="8" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="42">
@@ -10716,6 +12215,7 @@
       <c r="F8" s="50" t="s">
         <v>86</v>
       </c>
+      <c r="G8" s="85"/>
     </row>
     <row r="9" spans="1:11" s="8" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="41">
@@ -10736,6 +12236,9 @@
       <c r="F9" s="50" t="s">
         <v>220</v>
       </c>
+      <c r="G9" s="85">
+        <v>46254</v>
+      </c>
     </row>
     <row r="10" spans="1:11" s="8" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="42">
@@ -10755,6 +12258,9 @@
       </c>
       <c r="F10" s="50" t="s">
         <v>220</v>
+      </c>
+      <c r="G10" s="85">
+        <v>46254</v>
       </c>
     </row>
     <row r="11" spans="1:11" s="8" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
@@ -10790,7 +12296,7 @@
       <c r="E13" s="44"/>
       <c r="F13" s="41"/>
     </row>
-    <row r="14" spans="1:11" s="8" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="42">
         <v>8</v>
       </c>
@@ -10799,6 +12305,7 @@
       <c r="D14" s="44"/>
       <c r="E14" s="44"/>
       <c r="F14" s="41"/>
+      <c r="G14" s="24"/>
     </row>
     <row r="15" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="7"/>
@@ -11102,6 +12609,11 @@
   <mergeCells count="1">
     <mergeCell ref="A3:H3"/>
   </mergeCells>
+  <conditionalFormatting sqref="G8">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>LEFT(CELL("format",C8))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F8 F11:F14" xr:uid="{16120718-D99C-464F-A337-40BBD792BEA0}">
       <formula1>"20,40,45,50"</formula1>

--- a/Fiche de mouvement _08-2026.xlsx
+++ b/Fiche de mouvement _08-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lenovo\OneDrive\Documents\Samir\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E25C636D-87C3-4CFC-B6A1-B6CFC1F1CDCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{176391D1-43AE-46C3-BF5B-CF0AFC8E5022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="11" xr2:uid="{BEED4A70-B61E-4C8D-BAB3-F17C8E5D544F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="17" xr2:uid="{BEED4A70-B61E-4C8D-BAB3-F17C8E5D544F}"/>
   </bookViews>
   <sheets>
     <sheet name="DASHBOARD" sheetId="1" r:id="rId1"/>
@@ -30,6 +30,8 @@
     <sheet name="19-08" sheetId="15" r:id="rId15"/>
     <sheet name="20-08" sheetId="16" r:id="rId16"/>
     <sheet name="23-08" sheetId="17" r:id="rId17"/>
+    <sheet name="24-08" sheetId="18" r:id="rId18"/>
+    <sheet name="26-08" sheetId="19" r:id="rId19"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -52,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="827" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="917" uniqueCount="315">
   <si>
     <t>Date</t>
   </si>
@@ -926,6 +928,78 @@
   </si>
   <si>
     <t>Depotage</t>
+  </si>
+  <si>
+    <t>08436-585-14</t>
+  </si>
+  <si>
+    <t>002205-509-16</t>
+  </si>
+  <si>
+    <t>ECMU512820 /2</t>
+  </si>
+  <si>
+    <t>R9410054</t>
+  </si>
+  <si>
+    <t>TRLU948903 /4</t>
+  </si>
+  <si>
+    <t>L7956894</t>
+  </si>
+  <si>
+    <t>TCKU725483 /6</t>
+  </si>
+  <si>
+    <t>BD0235592</t>
+  </si>
+  <si>
+    <t>OOLU678904 /3</t>
+  </si>
+  <si>
+    <t>SYA5003483</t>
+  </si>
+  <si>
+    <t>ARKU855648 /7</t>
+  </si>
+  <si>
+    <t>B1779962</t>
+  </si>
+  <si>
+    <t>0078ICS0038</t>
+  </si>
+  <si>
+    <t>0147ICS0013</t>
+  </si>
+  <si>
+    <t>0147ICS0033</t>
+  </si>
+  <si>
+    <t>24/08/2026</t>
+  </si>
+  <si>
+    <t>002233-585-31</t>
+  </si>
+  <si>
+    <t>BMOU213576 /9</t>
+  </si>
+  <si>
+    <t>2134430</t>
+  </si>
+  <si>
+    <t>CXSU114000 /6</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>TCLU600602 /5</t>
+  </si>
+  <si>
+    <t>0152ICS0044</t>
+  </si>
+  <si>
+    <t>26/08/2026</t>
   </si>
 </sst>
 </file>
@@ -936,7 +1010,7 @@
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="165" formatCode="##&quot;/&quot;##&quot;/&quot;####"/>
   </numFmts>
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1070,6 +1144,20 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Segoe UI"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="9">
@@ -1362,7 +1450,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="86">
+  <cellXfs count="93">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1616,6 +1704,27 @@
     </xf>
     <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="14" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="23" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="24" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2093,6 +2202,116 @@
         <a:xfrm>
           <a:off x="0" y="1"/>
           <a:ext cx="2000250" cy="514349"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing17.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>476250</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Image 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D0802DD4-19F6-4BAC-8B53-BCD39A0CE73D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="1"/>
+          <a:ext cx="1666875" cy="457199"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing18.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>476250</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Image 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9DCD0176-5B64-40DA-AA14-90D580B17FB3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="1"/>
+          <a:ext cx="1666875" cy="457199"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3200,33 +3419,66 @@
       </c>
       <c r="C17" s="3">
         <f>'23-08'!H2</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D17" s="4">
         <f t="shared" si="7"/>
+        <v>2</v>
+      </c>
+      <c r="F17" s="3"/>
+    </row>
+    <row r="18" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A18" s="2">
+        <v>46258</v>
+      </c>
+      <c r="B18" s="3">
+        <f>'24-08'!H1</f>
+        <v>3</v>
+      </c>
+      <c r="C18" s="3">
+        <f>'24-08'!H2</f>
+        <v>1</v>
+      </c>
+      <c r="D18" s="4">
+        <f t="shared" ref="D18" si="8">SUM(B18:C18)</f>
+        <v>4</v>
+      </c>
+      <c r="F18" s="3"/>
+    </row>
+    <row r="19" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A19" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B19" s="3">
+        <f>'26-08'!H1</f>
+        <v>3</v>
+      </c>
+      <c r="C19" s="3">
+        <f>'26-08'!H2</f>
         <v>0</v>
       </c>
-      <c r="F17" s="3"/>
-    </row>
-    <row r="18" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A18" s="2"/>
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="4"/>
-      <c r="F18" s="3"/>
-    </row>
-    <row r="19" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A19" s="2"/>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="4"/>
+      <c r="D19" s="4">
+        <f t="shared" ref="D19:D20" si="9">SUM(B19:C19)</f>
+        <v>3</v>
+      </c>
       <c r="F19" s="3"/>
     </row>
     <row r="20" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A20" s="2"/>
-      <c r="B20" s="3"/>
-      <c r="C20" s="3"/>
-      <c r="D20" s="4"/>
+      <c r="A20" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B20" s="3">
+        <f>'24-08'!H3</f>
+        <v>0</v>
+      </c>
+      <c r="C20" s="3">
+        <f>'24-08'!H4</f>
+        <v>0</v>
+      </c>
+      <c r="D20" s="4">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
       <c r="F20" s="3"/>
     </row>
     <row r="21" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -3256,15 +3508,15 @@
       </c>
       <c r="B24" s="6">
         <f>SUM(B2:B23)</f>
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C24" s="6">
         <f>SUM(C2:C23)</f>
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D24" s="6">
         <f>SUM(D2:D23)</f>
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="E24" s="6"/>
       <c r="F24" s="6"/>
@@ -6538,8 +6790,9 @@
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.31496062992125984" right="0.31496062992125984" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -6610,7 +6863,7 @@
         <v>9</v>
       </c>
       <c r="G5" s="13">
-        <v>46253</v>
+        <v>46254</v>
       </c>
     </row>
     <row r="6" spans="1:11" s="8" customFormat="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -7078,8 +7331,9 @@
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.31496062992125984" right="0.31496062992125984" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -7130,7 +7384,7 @@
       </c>
       <c r="H2" s="9">
         <f>COUNTA(C19:C28)-F2</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I2" s="10" t="s">
         <v>6</v>
@@ -7176,7 +7430,7 @@
       <c r="E5" s="8"/>
       <c r="F5" s="8"/>
       <c r="G5" s="13">
-        <v>46253</v>
+        <v>46257</v>
       </c>
       <c r="H5" s="8"/>
       <c r="I5" s="8"/>
@@ -7366,36 +7620,58 @@
         <v>1</v>
       </c>
       <c r="B19" s="69">
-        <v>46254</v>
-      </c>
-      <c r="C19" s="47"/>
-      <c r="D19" s="41"/>
-      <c r="E19" s="50"/>
-      <c r="F19" s="50"/>
+        <v>46257</v>
+      </c>
+      <c r="C19" s="28" t="s">
+        <v>291</v>
+      </c>
+      <c r="D19" s="28" t="s">
+        <v>217</v>
+      </c>
+      <c r="E19" s="50">
+        <v>3960</v>
+      </c>
+      <c r="F19" s="50">
+        <v>45</v>
+      </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="36">
         <v>2</v>
       </c>
       <c r="B20" s="69">
-        <v>46254</v>
-      </c>
-      <c r="C20" s="38"/>
-      <c r="D20" s="44"/>
-      <c r="E20" s="44"/>
-      <c r="F20" s="50"/>
+        <v>46257</v>
+      </c>
+      <c r="C20" s="38" t="s">
+        <v>292</v>
+      </c>
+      <c r="D20" s="28" t="s">
+        <v>139</v>
+      </c>
+      <c r="E20" s="44">
+        <v>3905</v>
+      </c>
+      <c r="F20" s="50">
+        <v>40</v>
+      </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="36">
         <v>3</v>
       </c>
       <c r="B21" s="69">
-        <v>46254</v>
+        <v>46257</v>
       </c>
       <c r="C21" s="38"/>
-      <c r="D21" s="44"/>
-      <c r="E21" s="44"/>
-      <c r="F21" s="50"/>
+      <c r="D21" s="28" t="s">
+        <v>137</v>
+      </c>
+      <c r="E21" s="44">
+        <v>3906</v>
+      </c>
+      <c r="F21" s="50">
+        <v>40</v>
+      </c>
       <c r="G21" s="24" t="s">
         <v>42</v>
       </c>
@@ -7405,9 +7681,7 @@
       <c r="A22" s="36">
         <v>4</v>
       </c>
-      <c r="B22" s="69">
-        <v>46254</v>
-      </c>
+      <c r="B22" s="69"/>
       <c r="C22" s="38"/>
       <c r="D22" s="44"/>
       <c r="E22" s="44"/>
@@ -7810,6 +8084,1274 @@
   <phoneticPr fontId="13" type="noConversion"/>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F8:F14 F19:F22" xr:uid="{2017016A-DB0F-4C7A-A34F-906C9B5FB086}">
+      <formula1>"20,40,45,50"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.31496062992125984" right="0.31496062992125984" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{328C01C3-9DDA-4373-8DF5-84DACD1F525B}">
+  <dimension ref="A1:J46"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3.140625" style="24" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.7109375" style="24" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" style="24" customWidth="1"/>
+    <col min="4" max="4" width="19.140625" style="24" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="24" customWidth="1"/>
+    <col min="6" max="6" width="14" style="24" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.140625" style="24" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="11.42578125" style="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="7"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="9">
+        <f>COUNTIF(C8:C14,"&lt;&gt;")</f>
+        <v>3</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" s="8"/>
+    </row>
+    <row r="2" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="7"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="9">
+        <f>COUNTIFS(B19:B22,"&lt;&gt;",C19:C22,"VH")</f>
+        <v>0</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="9">
+        <f>COUNTA(C19:C28)-F2</f>
+        <v>1</v>
+      </c>
+      <c r="I2" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="J2" s="11">
+        <f>COUNTIF(H19:H24,"VIDE")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="70" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="70"/>
+      <c r="C3" s="70"/>
+      <c r="D3" s="70"/>
+      <c r="E3" s="70"/>
+      <c r="F3" s="70"/>
+      <c r="G3" s="70"/>
+      <c r="H3" s="70"/>
+      <c r="I3" s="8"/>
+      <c r="J3" s="8"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="7"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="8"/>
+    </row>
+    <row r="5" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="7"/>
+      <c r="B5" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="13">
+        <v>46258</v>
+      </c>
+      <c r="H5" s="8"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="8"/>
+    </row>
+    <row r="6" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="7"/>
+      <c r="B6" s="14"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8"/>
+      <c r="J6" s="8"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="42">
+        <v>2</v>
+      </c>
+      <c r="B8" s="41" t="s">
+        <v>303</v>
+      </c>
+      <c r="C8" s="86" t="s">
+        <v>306</v>
+      </c>
+      <c r="D8" s="44" t="s">
+        <v>297</v>
+      </c>
+      <c r="E8" s="44" t="s">
+        <v>298</v>
+      </c>
+      <c r="F8" s="50">
+        <v>40</v>
+      </c>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="41">
+        <v>3</v>
+      </c>
+      <c r="B9" s="51" t="s">
+        <v>304</v>
+      </c>
+      <c r="C9" s="86" t="s">
+        <v>306</v>
+      </c>
+      <c r="D9" s="50" t="s">
+        <v>299</v>
+      </c>
+      <c r="E9" s="50" t="s">
+        <v>300</v>
+      </c>
+      <c r="F9" s="50">
+        <v>40</v>
+      </c>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="8"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="42">
+        <v>4</v>
+      </c>
+      <c r="B10" s="51" t="s">
+        <v>305</v>
+      </c>
+      <c r="C10" s="86" t="s">
+        <v>306</v>
+      </c>
+      <c r="D10" s="50" t="s">
+        <v>301</v>
+      </c>
+      <c r="E10" s="50" t="s">
+        <v>302</v>
+      </c>
+      <c r="F10" s="50">
+        <v>40</v>
+      </c>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="42">
+        <v>5</v>
+      </c>
+      <c r="B11" s="51"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="50"/>
+      <c r="E11" s="50"/>
+      <c r="F11" s="50"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="41">
+        <v>6</v>
+      </c>
+      <c r="B12" s="51"/>
+      <c r="C12" s="27"/>
+      <c r="D12" s="50"/>
+      <c r="E12" s="50"/>
+      <c r="F12" s="50"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="41">
+        <v>7</v>
+      </c>
+      <c r="B13" s="51"/>
+      <c r="C13" s="27"/>
+      <c r="D13" s="44"/>
+      <c r="E13" s="44"/>
+      <c r="F13" s="41"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="8"/>
+      <c r="J13" s="8"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="42">
+        <v>8</v>
+      </c>
+      <c r="B14" s="41"/>
+      <c r="C14" s="27"/>
+      <c r="D14" s="44"/>
+      <c r="E14" s="44"/>
+      <c r="F14" s="41"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="8"/>
+    </row>
+    <row r="15" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="7"/>
+      <c r="B15" s="25"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="25"/>
+    </row>
+    <row r="16" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="7"/>
+      <c r="B16" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="G16" s="25"/>
+    </row>
+    <row r="17" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="7"/>
+      <c r="B17" s="14"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="8"/>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="B18" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="D18" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="E18" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="F18" s="17" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" s="36">
+        <v>1</v>
+      </c>
+      <c r="B19" s="86" t="s">
+        <v>306</v>
+      </c>
+      <c r="C19" s="28" t="s">
+        <v>307</v>
+      </c>
+      <c r="D19" s="28" t="s">
+        <v>269</v>
+      </c>
+      <c r="E19" s="50">
+        <v>3504</v>
+      </c>
+      <c r="F19" s="50">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" s="36">
+        <v>2</v>
+      </c>
+      <c r="B20" s="69"/>
+      <c r="C20" s="38"/>
+      <c r="D20" s="28"/>
+      <c r="E20" s="44"/>
+      <c r="F20" s="50"/>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" s="36">
+        <v>3</v>
+      </c>
+      <c r="B21" s="69"/>
+      <c r="C21" s="38"/>
+      <c r="D21" s="28"/>
+      <c r="E21" s="44"/>
+      <c r="F21" s="50"/>
+      <c r="G21" s="24" t="s">
+        <v>42</v>
+      </c>
+      <c r="J21" s="67"/>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" s="36">
+        <v>4</v>
+      </c>
+      <c r="B22" s="69"/>
+      <c r="C22" s="38"/>
+      <c r="D22" s="44"/>
+      <c r="E22" s="44"/>
+      <c r="F22" s="50"/>
+      <c r="J22" s="67"/>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" s="36">
+        <v>5</v>
+      </c>
+      <c r="B23" s="69"/>
+      <c r="C23" s="38"/>
+      <c r="D23" s="50"/>
+      <c r="E23" s="38"/>
+      <c r="F23" s="38"/>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" s="36">
+        <v>6</v>
+      </c>
+      <c r="B24" s="27"/>
+      <c r="C24" s="38"/>
+      <c r="D24" s="50"/>
+      <c r="E24" s="41"/>
+      <c r="F24" s="29"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" s="36">
+        <v>7</v>
+      </c>
+      <c r="B25" s="27"/>
+      <c r="C25" s="38"/>
+      <c r="D25" s="43"/>
+      <c r="E25" s="50"/>
+      <c r="F25" s="29"/>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" s="36">
+        <v>8</v>
+      </c>
+      <c r="B26" s="27"/>
+      <c r="C26" s="28"/>
+      <c r="D26" s="39"/>
+      <c r="E26" s="29"/>
+      <c r="F26" s="29"/>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" s="36">
+        <v>9</v>
+      </c>
+      <c r="B27" s="27"/>
+      <c r="C27" s="41"/>
+      <c r="D27" s="44"/>
+      <c r="E27" s="41"/>
+      <c r="F27" s="29"/>
+    </row>
+    <row r="28" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A28" s="36">
+        <v>10</v>
+      </c>
+      <c r="B28" s="27"/>
+      <c r="C28" s="41"/>
+      <c r="D28" s="44"/>
+      <c r="E28" s="41"/>
+      <c r="F28" s="29"/>
+      <c r="G28" s="25"/>
+    </row>
+    <row r="29" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A29" s="7"/>
+      <c r="B29" s="12"/>
+      <c r="C29" s="8"/>
+      <c r="D29" s="45"/>
+      <c r="E29" s="8"/>
+      <c r="F29" s="8"/>
+      <c r="G29" s="25"/>
+    </row>
+    <row r="30" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A30" s="7"/>
+      <c r="B30" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C30" s="8"/>
+      <c r="D30" s="45"/>
+      <c r="E30" s="8"/>
+      <c r="F30" s="8"/>
+      <c r="G30" s="25"/>
+    </row>
+    <row r="31" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="7"/>
+      <c r="B31" s="14"/>
+      <c r="C31" s="8"/>
+      <c r="D31" s="8"/>
+      <c r="E31" s="8"/>
+      <c r="F31" s="8"/>
+      <c r="G31" s="8"/>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="B32" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="C32" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="D32" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="E32" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="F32" s="17" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="41">
+        <v>1</v>
+      </c>
+      <c r="B33" s="69">
+        <v>46258</v>
+      </c>
+      <c r="C33" s="28" t="s">
+        <v>293</v>
+      </c>
+      <c r="D33" s="28" t="s">
+        <v>294</v>
+      </c>
+      <c r="E33" s="38">
+        <v>3579</v>
+      </c>
+      <c r="F33" s="28">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="41">
+        <v>2</v>
+      </c>
+      <c r="B34" s="69">
+        <v>46258</v>
+      </c>
+      <c r="C34" s="39" t="s">
+        <v>295</v>
+      </c>
+      <c r="D34" s="39" t="s">
+        <v>296</v>
+      </c>
+      <c r="E34" s="28">
+        <v>3571</v>
+      </c>
+      <c r="F34" s="28">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="41">
+        <v>3</v>
+      </c>
+      <c r="B35" s="27"/>
+      <c r="C35" s="44"/>
+      <c r="D35" s="44"/>
+      <c r="E35" s="38"/>
+      <c r="F35" s="28"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="41">
+        <v>4</v>
+      </c>
+      <c r="B36" s="27"/>
+      <c r="C36" s="44"/>
+      <c r="D36" s="44"/>
+      <c r="E36" s="38"/>
+      <c r="F36" s="28"/>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="41">
+        <v>5</v>
+      </c>
+      <c r="B37" s="27"/>
+      <c r="C37" s="44"/>
+      <c r="D37" s="44"/>
+      <c r="E37" s="38"/>
+      <c r="F37" s="28"/>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="41">
+        <v>6</v>
+      </c>
+      <c r="B38" s="27"/>
+      <c r="C38" s="44"/>
+      <c r="D38" s="44"/>
+      <c r="E38" s="38"/>
+      <c r="F38" s="28"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="41">
+        <v>7</v>
+      </c>
+      <c r="B39" s="27"/>
+      <c r="C39" s="44"/>
+      <c r="D39" s="44"/>
+      <c r="E39" s="38"/>
+      <c r="F39" s="28"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="41">
+        <v>8</v>
+      </c>
+      <c r="B40" s="27"/>
+      <c r="C40" s="44"/>
+      <c r="D40" s="44"/>
+      <c r="E40" s="38"/>
+      <c r="F40" s="28"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="41">
+        <v>9</v>
+      </c>
+      <c r="B41" s="27"/>
+      <c r="C41" s="44"/>
+      <c r="D41" s="44"/>
+      <c r="E41" s="38"/>
+      <c r="F41" s="28"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="41">
+        <v>10</v>
+      </c>
+      <c r="B42" s="27"/>
+      <c r="C42" s="44"/>
+      <c r="D42" s="44"/>
+      <c r="E42" s="38"/>
+      <c r="F42" s="28"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="41">
+        <v>11</v>
+      </c>
+      <c r="B43" s="27"/>
+      <c r="C43" s="44"/>
+      <c r="D43" s="44"/>
+      <c r="E43" s="38"/>
+      <c r="F43" s="28"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="41">
+        <v>12</v>
+      </c>
+      <c r="B44" s="27"/>
+      <c r="C44" s="44"/>
+      <c r="D44" s="44"/>
+      <c r="E44" s="38"/>
+      <c r="F44" s="28"/>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="41">
+        <v>13</v>
+      </c>
+      <c r="B45" s="27"/>
+      <c r="C45" s="44"/>
+      <c r="D45" s="44"/>
+      <c r="E45" s="38"/>
+      <c r="F45" s="28"/>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="41">
+        <v>14</v>
+      </c>
+      <c r="B46" s="27"/>
+      <c r="C46" s="44"/>
+      <c r="D46" s="44"/>
+      <c r="E46" s="38"/>
+      <c r="F46" s="28"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A3:H3"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F8:F14 F19:F22" xr:uid="{02F85F5D-B26B-4375-AF91-582762076C6C}">
+      <formula1>"20,40,45,50"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.31496062992125984" right="0.31496062992125984" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6BD127BC-4D25-4C59-8A03-CFE4A5FAB74B}">
+  <dimension ref="A1:J46"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3.140625" style="24" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.7109375" style="24" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" style="24" customWidth="1"/>
+    <col min="4" max="4" width="19.140625" style="24" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="24" customWidth="1"/>
+    <col min="6" max="6" width="14" style="24" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.140625" style="24" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="11.42578125" style="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="7"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="9">
+        <f>COUNTIF(C8:C14,"&lt;&gt;")</f>
+        <v>3</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" s="8"/>
+    </row>
+    <row r="2" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="7"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="9">
+        <f>COUNTIFS(B19:B22,"&lt;&gt;",C19:C22,"VH")</f>
+        <v>0</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="9">
+        <f>COUNTA(C19:C28)-F2</f>
+        <v>0</v>
+      </c>
+      <c r="I2" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="J2" s="11">
+        <f>COUNTIF(H19:H24,"VIDE")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="70" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="70"/>
+      <c r="C3" s="70"/>
+      <c r="D3" s="70"/>
+      <c r="E3" s="70"/>
+      <c r="F3" s="70"/>
+      <c r="G3" s="70"/>
+      <c r="H3" s="70"/>
+      <c r="I3" s="8"/>
+      <c r="J3" s="8"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="7"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="8"/>
+    </row>
+    <row r="5" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="7"/>
+      <c r="B5" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="13">
+        <v>46260</v>
+      </c>
+      <c r="H5" s="8"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="8"/>
+    </row>
+    <row r="6" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="7"/>
+      <c r="B6" s="14"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8"/>
+      <c r="J6" s="8"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="42">
+        <v>2</v>
+      </c>
+      <c r="B8" s="87" t="s">
+        <v>313</v>
+      </c>
+      <c r="C8" s="88" t="s">
+        <v>314</v>
+      </c>
+      <c r="D8" s="89" t="s">
+        <v>308</v>
+      </c>
+      <c r="E8" s="89" t="s">
+        <v>309</v>
+      </c>
+      <c r="F8" s="90">
+        <v>20</v>
+      </c>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="41">
+        <v>3</v>
+      </c>
+      <c r="B9" s="91" t="s">
+        <v>313</v>
+      </c>
+      <c r="C9" s="88" t="s">
+        <v>314</v>
+      </c>
+      <c r="D9" s="92" t="s">
+        <v>310</v>
+      </c>
+      <c r="E9" s="90" t="s">
+        <v>311</v>
+      </c>
+      <c r="F9" s="90" t="s">
+        <v>109</v>
+      </c>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="8"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="42">
+        <v>4</v>
+      </c>
+      <c r="B10" s="91" t="s">
+        <v>313</v>
+      </c>
+      <c r="C10" s="88" t="s">
+        <v>314</v>
+      </c>
+      <c r="D10" s="90" t="s">
+        <v>312</v>
+      </c>
+      <c r="E10" s="90" t="s">
+        <v>311</v>
+      </c>
+      <c r="F10" s="90" t="s">
+        <v>109</v>
+      </c>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="42">
+        <v>5</v>
+      </c>
+      <c r="B11" s="51"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="50"/>
+      <c r="E11" s="50"/>
+      <c r="F11" s="50"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="41">
+        <v>6</v>
+      </c>
+      <c r="B12" s="51"/>
+      <c r="C12" s="27"/>
+      <c r="D12" s="50"/>
+      <c r="E12" s="50"/>
+      <c r="F12" s="50"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="41">
+        <v>7</v>
+      </c>
+      <c r="B13" s="51"/>
+      <c r="C13" s="27"/>
+      <c r="D13" s="44"/>
+      <c r="E13" s="44"/>
+      <c r="F13" s="41"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="8"/>
+      <c r="J13" s="8"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="42">
+        <v>8</v>
+      </c>
+      <c r="B14" s="41"/>
+      <c r="C14" s="27"/>
+      <c r="D14" s="44"/>
+      <c r="E14" s="44"/>
+      <c r="F14" s="41"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="8"/>
+    </row>
+    <row r="15" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="7"/>
+      <c r="B15" s="25"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="25"/>
+    </row>
+    <row r="16" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="7"/>
+      <c r="B16" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="G16" s="25"/>
+    </row>
+    <row r="17" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="7"/>
+      <c r="B17" s="14"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="8"/>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="B18" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="D18" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="E18" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="F18" s="17" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" s="36">
+        <v>1</v>
+      </c>
+      <c r="B19" s="86"/>
+      <c r="C19" s="28"/>
+      <c r="D19" s="28"/>
+      <c r="E19" s="50"/>
+      <c r="F19" s="50"/>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" s="36">
+        <v>2</v>
+      </c>
+      <c r="B20" s="69"/>
+      <c r="C20" s="38"/>
+      <c r="D20" s="28"/>
+      <c r="E20" s="44"/>
+      <c r="F20" s="50"/>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" s="36">
+        <v>3</v>
+      </c>
+      <c r="B21" s="69"/>
+      <c r="C21" s="38"/>
+      <c r="D21" s="28"/>
+      <c r="E21" s="44"/>
+      <c r="F21" s="50"/>
+      <c r="G21" s="24" t="s">
+        <v>42</v>
+      </c>
+      <c r="J21" s="67"/>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" s="36">
+        <v>4</v>
+      </c>
+      <c r="B22" s="69"/>
+      <c r="C22" s="38"/>
+      <c r="D22" s="44"/>
+      <c r="E22" s="44"/>
+      <c r="F22" s="50"/>
+      <c r="J22" s="67"/>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" s="36">
+        <v>5</v>
+      </c>
+      <c r="B23" s="69"/>
+      <c r="C23" s="38"/>
+      <c r="D23" s="50"/>
+      <c r="E23" s="38"/>
+      <c r="F23" s="38"/>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" s="36">
+        <v>6</v>
+      </c>
+      <c r="B24" s="27"/>
+      <c r="C24" s="38"/>
+      <c r="D24" s="50"/>
+      <c r="E24" s="41"/>
+      <c r="F24" s="29"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" s="36">
+        <v>7</v>
+      </c>
+      <c r="B25" s="27"/>
+      <c r="C25" s="38"/>
+      <c r="D25" s="43"/>
+      <c r="E25" s="50"/>
+      <c r="F25" s="29"/>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" s="36">
+        <v>8</v>
+      </c>
+      <c r="B26" s="27"/>
+      <c r="C26" s="28"/>
+      <c r="D26" s="39"/>
+      <c r="E26" s="29"/>
+      <c r="F26" s="29"/>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" s="36">
+        <v>9</v>
+      </c>
+      <c r="B27" s="27"/>
+      <c r="C27" s="41"/>
+      <c r="D27" s="44"/>
+      <c r="E27" s="41"/>
+      <c r="F27" s="29"/>
+    </row>
+    <row r="28" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A28" s="36">
+        <v>10</v>
+      </c>
+      <c r="B28" s="27"/>
+      <c r="C28" s="41"/>
+      <c r="D28" s="44"/>
+      <c r="E28" s="41"/>
+      <c r="F28" s="29"/>
+      <c r="G28" s="25"/>
+    </row>
+    <row r="29" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A29" s="7"/>
+      <c r="B29" s="12"/>
+      <c r="C29" s="8"/>
+      <c r="D29" s="45"/>
+      <c r="E29" s="8"/>
+      <c r="F29" s="8"/>
+      <c r="G29" s="25"/>
+    </row>
+    <row r="30" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A30" s="7"/>
+      <c r="B30" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C30" s="8"/>
+      <c r="D30" s="45"/>
+      <c r="E30" s="8"/>
+      <c r="F30" s="8"/>
+      <c r="G30" s="25"/>
+    </row>
+    <row r="31" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="7"/>
+      <c r="B31" s="14"/>
+      <c r="C31" s="8"/>
+      <c r="D31" s="8"/>
+      <c r="E31" s="8"/>
+      <c r="F31" s="8"/>
+      <c r="G31" s="8"/>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="B32" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="C32" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="D32" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="E32" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="F32" s="17" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="41">
+        <v>1</v>
+      </c>
+      <c r="B33" s="69"/>
+      <c r="C33" s="28"/>
+      <c r="D33" s="28"/>
+      <c r="E33" s="38"/>
+      <c r="F33" s="28"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="41">
+        <v>2</v>
+      </c>
+      <c r="B34" s="69"/>
+      <c r="C34" s="39"/>
+      <c r="D34" s="39"/>
+      <c r="E34" s="28"/>
+      <c r="F34" s="28"/>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="41">
+        <v>3</v>
+      </c>
+      <c r="B35" s="27"/>
+      <c r="C35" s="44"/>
+      <c r="D35" s="44"/>
+      <c r="E35" s="38"/>
+      <c r="F35" s="28"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="41">
+        <v>4</v>
+      </c>
+      <c r="B36" s="27"/>
+      <c r="C36" s="44"/>
+      <c r="D36" s="44"/>
+      <c r="E36" s="38"/>
+      <c r="F36" s="28"/>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="41">
+        <v>5</v>
+      </c>
+      <c r="B37" s="27"/>
+      <c r="C37" s="44"/>
+      <c r="D37" s="44"/>
+      <c r="E37" s="38"/>
+      <c r="F37" s="28"/>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="41">
+        <v>6</v>
+      </c>
+      <c r="B38" s="27"/>
+      <c r="C38" s="44"/>
+      <c r="D38" s="44"/>
+      <c r="E38" s="38"/>
+      <c r="F38" s="28"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="41">
+        <v>7</v>
+      </c>
+      <c r="B39" s="27"/>
+      <c r="C39" s="44"/>
+      <c r="D39" s="44"/>
+      <c r="E39" s="38"/>
+      <c r="F39" s="28"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="41">
+        <v>8</v>
+      </c>
+      <c r="B40" s="27"/>
+      <c r="C40" s="44"/>
+      <c r="D40" s="44"/>
+      <c r="E40" s="38"/>
+      <c r="F40" s="28"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="41">
+        <v>9</v>
+      </c>
+      <c r="B41" s="27"/>
+      <c r="C41" s="44"/>
+      <c r="D41" s="44"/>
+      <c r="E41" s="38"/>
+      <c r="F41" s="28"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="41">
+        <v>10</v>
+      </c>
+      <c r="B42" s="27"/>
+      <c r="C42" s="44"/>
+      <c r="D42" s="44"/>
+      <c r="E42" s="38"/>
+      <c r="F42" s="28"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="41">
+        <v>11</v>
+      </c>
+      <c r="B43" s="27"/>
+      <c r="C43" s="44"/>
+      <c r="D43" s="44"/>
+      <c r="E43" s="38"/>
+      <c r="F43" s="28"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="41">
+        <v>12</v>
+      </c>
+      <c r="B44" s="27"/>
+      <c r="C44" s="44"/>
+      <c r="D44" s="44"/>
+      <c r="E44" s="38"/>
+      <c r="F44" s="28"/>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="41">
+        <v>13</v>
+      </c>
+      <c r="B45" s="27"/>
+      <c r="C45" s="44"/>
+      <c r="D45" s="44"/>
+      <c r="E45" s="38"/>
+      <c r="F45" s="28"/>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="41">
+        <v>14</v>
+      </c>
+      <c r="B46" s="27"/>
+      <c r="C46" s="44"/>
+      <c r="D46" s="44"/>
+      <c r="E46" s="38"/>
+      <c r="F46" s="28"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A3:H3"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F19:F22 F8:F14" xr:uid="{A9697C81-F16A-45F6-BFB9-47582A4526B1}">
       <formula1>"20,40,45,50"</formula1>
       <formula2>0</formula2>
     </dataValidation>

--- a/Fiche de mouvement _08-2026.xlsx
+++ b/Fiche de mouvement _08-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lenovo\OneDrive\Documents\Samir\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{176391D1-43AE-46C3-BF5B-CF0AFC8E5022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F10C62F4-D005-4EF0-B4D2-403523D4B38B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="17" xr2:uid="{BEED4A70-B61E-4C8D-BAB3-F17C8E5D544F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="7" activeTab="21" xr2:uid="{BEED4A70-B61E-4C8D-BAB3-F17C8E5D544F}"/>
   </bookViews>
   <sheets>
     <sheet name="DASHBOARD" sheetId="1" r:id="rId1"/>
@@ -32,6 +32,9 @@
     <sheet name="23-08" sheetId="17" r:id="rId17"/>
     <sheet name="24-08" sheetId="18" r:id="rId18"/>
     <sheet name="26-08" sheetId="19" r:id="rId19"/>
+    <sheet name="27-08" sheetId="20" r:id="rId20"/>
+    <sheet name="30-08" sheetId="21" r:id="rId21"/>
+    <sheet name="31-08" sheetId="22" r:id="rId22"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -54,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="917" uniqueCount="315">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1020" uniqueCount="332">
   <si>
     <t>Date</t>
   </si>
@@ -1000,6 +1003,57 @@
   </si>
   <si>
     <t>26/08/2026</t>
+  </si>
+  <si>
+    <t>00028-515-31</t>
+  </si>
+  <si>
+    <t>000127-516-31</t>
+  </si>
+  <si>
+    <t>00037-517-31</t>
+  </si>
+  <si>
+    <t>ECMU290316 /3</t>
+  </si>
+  <si>
+    <t>ECMU291655 /6</t>
+  </si>
+  <si>
+    <t>ECMU291755 /2</t>
+  </si>
+  <si>
+    <t>ECMU295555 /2</t>
+  </si>
+  <si>
+    <t>H5968384</t>
+  </si>
+  <si>
+    <t>H3680151</t>
+  </si>
+  <si>
+    <t>H5100744</t>
+  </si>
+  <si>
+    <t>H5966711</t>
+  </si>
+  <si>
+    <t>02145-588-31</t>
+  </si>
+  <si>
+    <t>001766-588-31</t>
+  </si>
+  <si>
+    <t>00582-510-31</t>
+  </si>
+  <si>
+    <t>001450-590-31</t>
+  </si>
+  <si>
+    <t>CAIU873171 /8</t>
+  </si>
+  <si>
+    <t>MEDU733219 /1</t>
   </si>
 </sst>
 </file>
@@ -1657,10 +1711,34 @@
     <xf numFmtId="14" fontId="10" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="14" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="23" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="24" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="16" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1699,31 +1777,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="14" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="23" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="24" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2323,6 +2377,61 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing19.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>476250</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Image 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BBC941E9-D619-4EBC-9E30-24FFA43E83B6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="1"/>
+          <a:ext cx="1666875" cy="476249"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
@@ -2367,6 +2476,116 @@
         <a:xfrm>
           <a:off x="0" y="1"/>
           <a:ext cx="2000250" cy="514349"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing20.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>476250</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Image 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2C92AA50-E649-41DF-8977-44E12A34905B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="1"/>
+          <a:ext cx="1666875" cy="495299"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing21.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>476250</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Image 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D915C428-BEDE-4DDC-9392-BB50FE3C3B69}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="1"/>
+          <a:ext cx="1666875" cy="514349"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3455,11 +3674,11 @@
       </c>
       <c r="C19" s="3">
         <f>'26-08'!H2</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D19" s="4">
         <f t="shared" ref="D19:D20" si="9">SUM(B19:C19)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F19" s="3"/>
     </row>
@@ -3512,11 +3731,11 @@
       </c>
       <c r="C24" s="6">
         <f>SUM(C2:C23)</f>
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D24" s="6">
         <f>SUM(D2:D23)</f>
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E24" s="6"/>
       <c r="F24" s="6"/>
@@ -3573,16 +3792,16 @@
       </c>
     </row>
     <row r="3" spans="1:11" s="8" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="70" t="s">
+      <c r="A3" s="79" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="70"/>
-      <c r="C3" s="70"/>
-      <c r="D3" s="70"/>
-      <c r="E3" s="70"/>
-      <c r="F3" s="70"/>
-      <c r="G3" s="70"/>
-      <c r="H3" s="70"/>
+      <c r="B3" s="79"/>
+      <c r="C3" s="79"/>
+      <c r="D3" s="79"/>
+      <c r="E3" s="79"/>
+      <c r="F3" s="79"/>
+      <c r="G3" s="79"/>
+      <c r="H3" s="79"/>
     </row>
     <row r="4" spans="1:11" s="8" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="7"/>
@@ -3624,7 +3843,7 @@
       <c r="A8" s="42">
         <v>2</v>
       </c>
-      <c r="B8" s="82" t="s">
+      <c r="B8" s="90" t="s">
         <v>223</v>
       </c>
       <c r="C8" s="27">
@@ -3644,7 +3863,7 @@
       <c r="A9" s="41">
         <v>3</v>
       </c>
-      <c r="B9" s="83"/>
+      <c r="B9" s="91"/>
       <c r="C9" s="27">
         <v>46246</v>
       </c>
@@ -4080,16 +4299,16 @@
       </c>
     </row>
     <row r="3" spans="1:11" s="8" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="70" t="s">
+      <c r="A3" s="79" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="70"/>
-      <c r="C3" s="70"/>
-      <c r="D3" s="70"/>
-      <c r="E3" s="70"/>
-      <c r="F3" s="70"/>
-      <c r="G3" s="70"/>
-      <c r="H3" s="70"/>
+      <c r="B3" s="79"/>
+      <c r="C3" s="79"/>
+      <c r="D3" s="79"/>
+      <c r="E3" s="79"/>
+      <c r="F3" s="79"/>
+      <c r="G3" s="79"/>
+      <c r="H3" s="79"/>
     </row>
     <row r="4" spans="1:11" s="8" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="7"/>
@@ -4574,16 +4793,16 @@
       </c>
     </row>
     <row r="3" spans="1:11" s="8" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="70" t="s">
+      <c r="A3" s="79" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="70"/>
-      <c r="C3" s="70"/>
-      <c r="D3" s="70"/>
-      <c r="E3" s="70"/>
-      <c r="F3" s="70"/>
-      <c r="G3" s="70"/>
-      <c r="H3" s="70"/>
+      <c r="B3" s="79"/>
+      <c r="C3" s="79"/>
+      <c r="D3" s="79"/>
+      <c r="E3" s="79"/>
+      <c r="F3" s="79"/>
+      <c r="G3" s="79"/>
+      <c r="H3" s="79"/>
     </row>
     <row r="4" spans="1:11" s="8" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="7"/>
@@ -5137,16 +5356,16 @@
       </c>
     </row>
     <row r="3" spans="1:14" s="8" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="70" t="s">
+      <c r="A3" s="79" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="70"/>
-      <c r="C3" s="70"/>
-      <c r="D3" s="70"/>
-      <c r="E3" s="70"/>
-      <c r="F3" s="70"/>
-      <c r="G3" s="70"/>
-      <c r="H3" s="70"/>
+      <c r="B3" s="79"/>
+      <c r="C3" s="79"/>
+      <c r="D3" s="79"/>
+      <c r="E3" s="79"/>
+      <c r="F3" s="79"/>
+      <c r="G3" s="79"/>
+      <c r="H3" s="79"/>
     </row>
     <row r="4" spans="1:14" s="8" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="7"/>
@@ -5621,16 +5840,16 @@
       </c>
     </row>
     <row r="3" spans="1:11" s="8" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="70" t="s">
+      <c r="A3" s="79" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="70"/>
-      <c r="C3" s="70"/>
-      <c r="D3" s="70"/>
-      <c r="E3" s="70"/>
-      <c r="F3" s="70"/>
-      <c r="G3" s="70"/>
-      <c r="H3" s="70"/>
+      <c r="B3" s="79"/>
+      <c r="C3" s="79"/>
+      <c r="D3" s="79"/>
+      <c r="E3" s="79"/>
+      <c r="F3" s="79"/>
+      <c r="G3" s="79"/>
+      <c r="H3" s="79"/>
     </row>
     <row r="4" spans="1:11" s="8" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="7"/>
@@ -6175,16 +6394,16 @@
       </c>
     </row>
     <row r="3" spans="1:11" s="8" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="70" t="s">
+      <c r="A3" s="79" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="70"/>
-      <c r="C3" s="70"/>
-      <c r="D3" s="70"/>
-      <c r="E3" s="70"/>
-      <c r="F3" s="70"/>
-      <c r="G3" s="70"/>
-      <c r="H3" s="70"/>
+      <c r="B3" s="79"/>
+      <c r="C3" s="79"/>
+      <c r="D3" s="79"/>
+      <c r="E3" s="79"/>
+      <c r="F3" s="79"/>
+      <c r="G3" s="79"/>
+      <c r="H3" s="79"/>
     </row>
     <row r="4" spans="1:11" s="8" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="7"/>
@@ -6226,7 +6445,7 @@
       <c r="A8" s="42">
         <v>2</v>
       </c>
-      <c r="B8" s="71" t="s">
+      <c r="B8" s="92" t="s">
         <v>257</v>
       </c>
       <c r="C8" s="27">
@@ -6246,7 +6465,7 @@
       <c r="A9" s="41">
         <v>3</v>
       </c>
-      <c r="B9" s="71"/>
+      <c r="B9" s="92"/>
       <c r="C9" s="27">
         <v>46253</v>
       </c>
@@ -6843,16 +7062,16 @@
       </c>
     </row>
     <row r="3" spans="1:11" s="8" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="70" t="s">
+      <c r="A3" s="79" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="70"/>
-      <c r="C3" s="70"/>
-      <c r="D3" s="70"/>
-      <c r="E3" s="70"/>
-      <c r="F3" s="70"/>
-      <c r="G3" s="70"/>
-      <c r="H3" s="70"/>
+      <c r="B3" s="79"/>
+      <c r="C3" s="79"/>
+      <c r="D3" s="79"/>
+      <c r="E3" s="79"/>
+      <c r="F3" s="79"/>
+      <c r="G3" s="79"/>
+      <c r="H3" s="79"/>
     </row>
     <row r="4" spans="1:11" s="8" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="7"/>
@@ -6894,7 +7113,7 @@
       <c r="A8" s="42">
         <v>2</v>
       </c>
-      <c r="B8" s="71"/>
+      <c r="B8" s="92"/>
       <c r="C8" s="27"/>
       <c r="D8" s="44"/>
       <c r="E8" s="44"/>
@@ -6904,7 +7123,7 @@
       <c r="A9" s="41">
         <v>3</v>
       </c>
-      <c r="B9" s="71"/>
+      <c r="B9" s="92"/>
       <c r="C9" s="27"/>
       <c r="D9" s="50"/>
       <c r="E9" s="50"/>
@@ -7395,16 +7614,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="70" t="s">
+      <c r="A3" s="79" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="70"/>
-      <c r="C3" s="70"/>
-      <c r="D3" s="70"/>
-      <c r="E3" s="70"/>
-      <c r="F3" s="70"/>
-      <c r="G3" s="70"/>
-      <c r="H3" s="70"/>
+      <c r="B3" s="79"/>
+      <c r="C3" s="79"/>
+      <c r="D3" s="79"/>
+      <c r="E3" s="79"/>
+      <c r="F3" s="79"/>
+      <c r="G3" s="79"/>
+      <c r="H3" s="79"/>
       <c r="I3" s="8"/>
       <c r="J3" s="8"/>
     </row>
@@ -7476,7 +7695,7 @@
       <c r="A8" s="42">
         <v>2</v>
       </c>
-      <c r="B8" s="71"/>
+      <c r="B8" s="92"/>
       <c r="C8" s="27"/>
       <c r="D8" s="44"/>
       <c r="E8" s="44"/>
@@ -7490,7 +7709,7 @@
       <c r="A9" s="41">
         <v>3</v>
       </c>
-      <c r="B9" s="71"/>
+      <c r="B9" s="92"/>
       <c r="C9" s="27"/>
       <c r="D9" s="50"/>
       <c r="E9" s="50"/>
@@ -7805,7 +8024,7 @@
       <c r="B33" s="27">
         <v>46257</v>
       </c>
-      <c r="C33" s="84" t="s">
+      <c r="C33" s="70" t="s">
         <v>275</v>
       </c>
       <c r="D33" s="44">
@@ -7825,7 +8044,7 @@
       <c r="B34" s="27">
         <v>46257</v>
       </c>
-      <c r="C34" s="84" t="s">
+      <c r="C34" s="70" t="s">
         <v>276</v>
       </c>
       <c r="D34" s="44">
@@ -8152,16 +8371,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="70" t="s">
+      <c r="A3" s="79" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="70"/>
-      <c r="C3" s="70"/>
-      <c r="D3" s="70"/>
-      <c r="E3" s="70"/>
-      <c r="F3" s="70"/>
-      <c r="G3" s="70"/>
-      <c r="H3" s="70"/>
+      <c r="B3" s="79"/>
+      <c r="C3" s="79"/>
+      <c r="D3" s="79"/>
+      <c r="E3" s="79"/>
+      <c r="F3" s="79"/>
+      <c r="G3" s="79"/>
+      <c r="H3" s="79"/>
       <c r="I3" s="8"/>
       <c r="J3" s="8"/>
     </row>
@@ -8236,7 +8455,7 @@
       <c r="B8" s="41" t="s">
         <v>303</v>
       </c>
-      <c r="C8" s="86" t="s">
+      <c r="C8" s="72" t="s">
         <v>306</v>
       </c>
       <c r="D8" s="44" t="s">
@@ -8260,7 +8479,7 @@
       <c r="B9" s="51" t="s">
         <v>304</v>
       </c>
-      <c r="C9" s="86" t="s">
+      <c r="C9" s="72" t="s">
         <v>306</v>
       </c>
       <c r="D9" s="50" t="s">
@@ -8284,7 +8503,7 @@
       <c r="B10" s="51" t="s">
         <v>305</v>
       </c>
-      <c r="C10" s="86" t="s">
+      <c r="C10" s="72" t="s">
         <v>306</v>
       </c>
       <c r="D10" s="50" t="s">
@@ -8406,7 +8625,7 @@
       <c r="A19" s="36">
         <v>1</v>
       </c>
-      <c r="B19" s="86" t="s">
+      <c r="B19" s="72" t="s">
         <v>306</v>
       </c>
       <c r="C19" s="28" t="s">
@@ -8790,7 +9009,7 @@
       </c>
       <c r="H2" s="9">
         <f>COUNTA(C19:C28)-F2</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I2" s="10" t="s">
         <v>6</v>
@@ -8801,16 +9020,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="70" t="s">
+      <c r="A3" s="79" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="70"/>
-      <c r="C3" s="70"/>
-      <c r="D3" s="70"/>
-      <c r="E3" s="70"/>
-      <c r="F3" s="70"/>
-      <c r="G3" s="70"/>
-      <c r="H3" s="70"/>
+      <c r="B3" s="79"/>
+      <c r="C3" s="79"/>
+      <c r="D3" s="79"/>
+      <c r="E3" s="79"/>
+      <c r="F3" s="79"/>
+      <c r="G3" s="79"/>
+      <c r="H3" s="79"/>
       <c r="I3" s="8"/>
       <c r="J3" s="8"/>
     </row>
@@ -8882,19 +9101,19 @@
       <c r="A8" s="42">
         <v>2</v>
       </c>
-      <c r="B8" s="87" t="s">
+      <c r="B8" s="73" t="s">
         <v>313</v>
       </c>
-      <c r="C8" s="88" t="s">
+      <c r="C8" s="74" t="s">
         <v>314</v>
       </c>
-      <c r="D8" s="89" t="s">
+      <c r="D8" s="75" t="s">
         <v>308</v>
       </c>
-      <c r="E8" s="89" t="s">
+      <c r="E8" s="75" t="s">
         <v>309</v>
       </c>
-      <c r="F8" s="90">
+      <c r="F8" s="76">
         <v>20</v>
       </c>
       <c r="G8" s="8"/>
@@ -8906,19 +9125,19 @@
       <c r="A9" s="41">
         <v>3</v>
       </c>
-      <c r="B9" s="91" t="s">
+      <c r="B9" s="77" t="s">
         <v>313</v>
       </c>
-      <c r="C9" s="88" t="s">
+      <c r="C9" s="74" t="s">
         <v>314</v>
       </c>
-      <c r="D9" s="92" t="s">
+      <c r="D9" s="78" t="s">
         <v>310</v>
       </c>
-      <c r="E9" s="90" t="s">
+      <c r="E9" s="76" t="s">
         <v>311</v>
       </c>
-      <c r="F9" s="90" t="s">
+      <c r="F9" s="76" t="s">
         <v>109</v>
       </c>
       <c r="G9" s="8"/>
@@ -8930,19 +9149,19 @@
       <c r="A10" s="42">
         <v>4</v>
       </c>
-      <c r="B10" s="91" t="s">
+      <c r="B10" s="77" t="s">
         <v>313</v>
       </c>
-      <c r="C10" s="88" t="s">
+      <c r="C10" s="74" t="s">
         <v>314</v>
       </c>
-      <c r="D10" s="90" t="s">
+      <c r="D10" s="76" t="s">
         <v>312</v>
       </c>
-      <c r="E10" s="90" t="s">
+      <c r="E10" s="76" t="s">
         <v>311</v>
       </c>
-      <c r="F10" s="90" t="s">
+      <c r="F10" s="76" t="s">
         <v>109</v>
       </c>
       <c r="G10" s="8"/>
@@ -9052,41 +9271,71 @@
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" s="36">
+      <c r="A19" s="41">
         <v>1</v>
       </c>
-      <c r="B19" s="86"/>
-      <c r="C19" s="28"/>
-      <c r="D19" s="28"/>
-      <c r="E19" s="50"/>
-      <c r="F19" s="50"/>
+      <c r="B19" s="72" t="s">
+        <v>314</v>
+      </c>
+      <c r="C19" s="28" t="s">
+        <v>315</v>
+      </c>
+      <c r="D19" s="43" t="s">
+        <v>125</v>
+      </c>
+      <c r="E19" s="50">
+        <v>3513</v>
+      </c>
+      <c r="F19" s="50">
+        <v>40</v>
+      </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" s="36">
+      <c r="A20" s="41">
         <v>2</v>
       </c>
-      <c r="B20" s="69"/>
-      <c r="C20" s="38"/>
-      <c r="D20" s="28"/>
-      <c r="E20" s="44"/>
-      <c r="F20" s="50"/>
+      <c r="B20" s="72" t="s">
+        <v>314</v>
+      </c>
+      <c r="C20" s="38" t="s">
+        <v>316</v>
+      </c>
+      <c r="D20" s="39" t="s">
+        <v>127</v>
+      </c>
+      <c r="E20" s="28">
+        <v>3514</v>
+      </c>
+      <c r="F20" s="50">
+        <v>20</v>
+      </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" s="36">
+      <c r="A21" s="41">
         <v>3</v>
       </c>
-      <c r="B21" s="69"/>
-      <c r="C21" s="38"/>
-      <c r="D21" s="28"/>
-      <c r="E21" s="44"/>
-      <c r="F21" s="50"/>
+      <c r="B21" s="72" t="s">
+        <v>314</v>
+      </c>
+      <c r="C21" s="38" t="s">
+        <v>317</v>
+      </c>
+      <c r="D21" s="43" t="s">
+        <v>129</v>
+      </c>
+      <c r="E21" s="44">
+        <v>3515</v>
+      </c>
+      <c r="F21" s="50">
+        <v>40</v>
+      </c>
       <c r="G21" s="24" t="s">
         <v>42</v>
       </c>
       <c r="J21" s="67"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22" s="36">
+      <c r="A22" s="41">
         <v>4</v>
       </c>
       <c r="B22" s="69"/>
@@ -9356,8 +9605,9 @@
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.31496062992125984" right="0.31496062992125984" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -9408,16 +9658,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="8" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="70" t="s">
+      <c r="A3" s="79" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="70"/>
-      <c r="C3" s="70"/>
-      <c r="D3" s="70"/>
-      <c r="E3" s="70"/>
-      <c r="F3" s="70"/>
-      <c r="G3" s="70"/>
-      <c r="H3" s="70"/>
+      <c r="B3" s="79"/>
+      <c r="C3" s="79"/>
+      <c r="D3" s="79"/>
+      <c r="E3" s="79"/>
+      <c r="F3" s="79"/>
+      <c r="G3" s="79"/>
+      <c r="H3" s="79"/>
     </row>
     <row r="4" spans="1:10" s="8" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="7"/>
@@ -9917,6 +10167,1850 @@
   <pageMargins left="0.31496062992125984" right="0.11811023622047245" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
   <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3DAB930-3DD5-41A6-9372-ACDA10C359DB}">
+  <dimension ref="A1:J46"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3.140625" style="24" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.7109375" style="24" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" style="24" customWidth="1"/>
+    <col min="4" max="4" width="19.140625" style="24" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="24" customWidth="1"/>
+    <col min="6" max="6" width="14" style="24" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.140625" style="24" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="11.42578125" style="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="7"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="9">
+        <f>COUNTIF(C8:C14,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" s="8"/>
+    </row>
+    <row r="2" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="7"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="9">
+        <f>COUNTIFS(B19:B22,"&lt;&gt;",C19:C22,"VH")</f>
+        <v>0</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="9">
+        <f>COUNTA(C19:C28)-F2</f>
+        <v>4</v>
+      </c>
+      <c r="I2" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="J2" s="11">
+        <f>COUNTIF(H19:H24,"VIDE")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="79" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="79"/>
+      <c r="C3" s="79"/>
+      <c r="D3" s="79"/>
+      <c r="E3" s="79"/>
+      <c r="F3" s="79"/>
+      <c r="G3" s="79"/>
+      <c r="H3" s="79"/>
+      <c r="I3" s="8"/>
+      <c r="J3" s="8"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="7"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="8"/>
+    </row>
+    <row r="5" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="7"/>
+      <c r="B5" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="13">
+        <v>46261</v>
+      </c>
+      <c r="H5" s="8"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="8"/>
+    </row>
+    <row r="6" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="7"/>
+      <c r="B6" s="14"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8"/>
+      <c r="J6" s="8"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="42">
+        <v>2</v>
+      </c>
+      <c r="B8" s="73"/>
+      <c r="C8" s="74"/>
+      <c r="D8" s="75"/>
+      <c r="E8" s="75"/>
+      <c r="F8" s="76"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="41">
+        <v>3</v>
+      </c>
+      <c r="B9" s="77"/>
+      <c r="C9" s="74"/>
+      <c r="D9" s="78"/>
+      <c r="E9" s="76"/>
+      <c r="F9" s="76"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="8"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="42">
+        <v>4</v>
+      </c>
+      <c r="B10" s="77"/>
+      <c r="C10" s="74"/>
+      <c r="D10" s="76"/>
+      <c r="E10" s="76"/>
+      <c r="F10" s="76"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="42">
+        <v>5</v>
+      </c>
+      <c r="B11" s="51"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="50"/>
+      <c r="E11" s="50"/>
+      <c r="F11" s="50"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="41">
+        <v>6</v>
+      </c>
+      <c r="B12" s="51"/>
+      <c r="C12" s="27"/>
+      <c r="D12" s="50"/>
+      <c r="E12" s="50"/>
+      <c r="F12" s="50"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="41">
+        <v>7</v>
+      </c>
+      <c r="B13" s="51"/>
+      <c r="C13" s="27"/>
+      <c r="D13" s="44"/>
+      <c r="E13" s="44"/>
+      <c r="F13" s="41"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="8"/>
+      <c r="J13" s="8"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="42">
+        <v>8</v>
+      </c>
+      <c r="B14" s="41"/>
+      <c r="C14" s="27"/>
+      <c r="D14" s="44"/>
+      <c r="E14" s="44"/>
+      <c r="F14" s="41"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="8"/>
+    </row>
+    <row r="15" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="7"/>
+      <c r="B15" s="25"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="25"/>
+    </row>
+    <row r="16" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="7"/>
+      <c r="B16" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="G16" s="25"/>
+    </row>
+    <row r="17" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="7"/>
+      <c r="B17" s="14"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="8"/>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="B18" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="D18" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="E18" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="F18" s="17" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" s="41">
+        <v>1</v>
+      </c>
+      <c r="B19" s="72">
+        <v>46261</v>
+      </c>
+      <c r="C19" s="38" t="s">
+        <v>329</v>
+      </c>
+      <c r="D19" s="43" t="s">
+        <v>318</v>
+      </c>
+      <c r="E19" s="50" t="s">
+        <v>322</v>
+      </c>
+      <c r="F19" s="50">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" s="41">
+        <v>2</v>
+      </c>
+      <c r="B20" s="72">
+        <v>46261</v>
+      </c>
+      <c r="C20" s="38" t="s">
+        <v>326</v>
+      </c>
+      <c r="D20" s="39" t="s">
+        <v>319</v>
+      </c>
+      <c r="E20" s="28" t="s">
+        <v>323</v>
+      </c>
+      <c r="F20" s="50">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" s="41">
+        <v>3</v>
+      </c>
+      <c r="B21" s="72">
+        <v>46261</v>
+      </c>
+      <c r="C21" s="28" t="s">
+        <v>327</v>
+      </c>
+      <c r="D21" s="43" t="s">
+        <v>320</v>
+      </c>
+      <c r="E21" s="44" t="s">
+        <v>324</v>
+      </c>
+      <c r="F21" s="50">
+        <v>20</v>
+      </c>
+      <c r="G21" s="24" t="s">
+        <v>42</v>
+      </c>
+      <c r="J21" s="67"/>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" s="41">
+        <v>4</v>
+      </c>
+      <c r="B22" s="72">
+        <v>46261</v>
+      </c>
+      <c r="C22" s="28" t="s">
+        <v>328</v>
+      </c>
+      <c r="D22" s="44" t="s">
+        <v>321</v>
+      </c>
+      <c r="E22" s="44" t="s">
+        <v>325</v>
+      </c>
+      <c r="F22" s="50">
+        <v>20</v>
+      </c>
+      <c r="J22" s="67"/>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" s="36">
+        <v>5</v>
+      </c>
+      <c r="B23" s="69"/>
+      <c r="D23" s="50"/>
+      <c r="E23" s="38"/>
+      <c r="F23" s="38"/>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" s="36">
+        <v>6</v>
+      </c>
+      <c r="B24" s="27"/>
+      <c r="C24" s="38"/>
+      <c r="D24" s="50"/>
+      <c r="E24" s="41"/>
+      <c r="F24" s="29"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" s="36">
+        <v>7</v>
+      </c>
+      <c r="B25" s="27"/>
+      <c r="C25" s="38"/>
+      <c r="D25" s="43"/>
+      <c r="E25" s="50"/>
+      <c r="F25" s="29"/>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" s="36">
+        <v>8</v>
+      </c>
+      <c r="B26" s="27"/>
+      <c r="C26" s="28"/>
+      <c r="D26" s="39"/>
+      <c r="E26" s="29"/>
+      <c r="F26" s="29"/>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" s="36">
+        <v>9</v>
+      </c>
+      <c r="B27" s="27"/>
+      <c r="C27" s="41"/>
+      <c r="D27" s="44"/>
+      <c r="E27" s="41"/>
+      <c r="F27" s="29"/>
+    </row>
+    <row r="28" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A28" s="36">
+        <v>10</v>
+      </c>
+      <c r="B28" s="27"/>
+      <c r="C28" s="41"/>
+      <c r="D28" s="44"/>
+      <c r="E28" s="41"/>
+      <c r="F28" s="29"/>
+      <c r="G28" s="25"/>
+    </row>
+    <row r="29" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A29" s="7"/>
+      <c r="B29" s="12"/>
+      <c r="C29" s="8"/>
+      <c r="D29" s="45"/>
+      <c r="E29" s="8"/>
+      <c r="F29" s="8"/>
+      <c r="G29" s="25"/>
+    </row>
+    <row r="30" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A30" s="7"/>
+      <c r="B30" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C30" s="8"/>
+      <c r="D30" s="45"/>
+      <c r="E30" s="8"/>
+      <c r="F30" s="8"/>
+      <c r="G30" s="25"/>
+    </row>
+    <row r="31" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="7"/>
+      <c r="B31" s="14"/>
+      <c r="C31" s="8"/>
+      <c r="D31" s="8"/>
+      <c r="E31" s="8"/>
+      <c r="F31" s="8"/>
+      <c r="G31" s="8"/>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="B32" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="C32" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="D32" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="E32" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="F32" s="17" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="41">
+        <v>1</v>
+      </c>
+      <c r="B33" s="69"/>
+      <c r="C33" s="28"/>
+      <c r="D33" s="28"/>
+      <c r="E33" s="38"/>
+      <c r="F33" s="28"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="41">
+        <v>2</v>
+      </c>
+      <c r="B34" s="69"/>
+      <c r="C34" s="39"/>
+      <c r="D34" s="39"/>
+      <c r="E34" s="28"/>
+      <c r="F34" s="28"/>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="41">
+        <v>3</v>
+      </c>
+      <c r="B35" s="27"/>
+      <c r="C35" s="44"/>
+      <c r="D35" s="44"/>
+      <c r="E35" s="38"/>
+      <c r="F35" s="28"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="41">
+        <v>4</v>
+      </c>
+      <c r="B36" s="27"/>
+      <c r="C36" s="44"/>
+      <c r="D36" s="44"/>
+      <c r="E36" s="38"/>
+      <c r="F36" s="28"/>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="41">
+        <v>5</v>
+      </c>
+      <c r="B37" s="27"/>
+      <c r="C37" s="44"/>
+      <c r="D37" s="44"/>
+      <c r="E37" s="38"/>
+      <c r="F37" s="28"/>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="41">
+        <v>6</v>
+      </c>
+      <c r="B38" s="27"/>
+      <c r="C38" s="44"/>
+      <c r="D38" s="44"/>
+      <c r="E38" s="38"/>
+      <c r="F38" s="28"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="41">
+        <v>7</v>
+      </c>
+      <c r="B39" s="27"/>
+      <c r="C39" s="44"/>
+      <c r="D39" s="44"/>
+      <c r="E39" s="38"/>
+      <c r="F39" s="28"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="41">
+        <v>8</v>
+      </c>
+      <c r="B40" s="27"/>
+      <c r="C40" s="44"/>
+      <c r="D40" s="44"/>
+      <c r="E40" s="38"/>
+      <c r="F40" s="28"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="41">
+        <v>9</v>
+      </c>
+      <c r="B41" s="27"/>
+      <c r="C41" s="44"/>
+      <c r="D41" s="44"/>
+      <c r="E41" s="38"/>
+      <c r="F41" s="28"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="41">
+        <v>10</v>
+      </c>
+      <c r="B42" s="27"/>
+      <c r="C42" s="44"/>
+      <c r="D42" s="44"/>
+      <c r="E42" s="38"/>
+      <c r="F42" s="28"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="41">
+        <v>11</v>
+      </c>
+      <c r="B43" s="27"/>
+      <c r="C43" s="44"/>
+      <c r="D43" s="44"/>
+      <c r="E43" s="38"/>
+      <c r="F43" s="28"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="41">
+        <v>12</v>
+      </c>
+      <c r="B44" s="27"/>
+      <c r="C44" s="44"/>
+      <c r="D44" s="44"/>
+      <c r="E44" s="38"/>
+      <c r="F44" s="28"/>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="41">
+        <v>13</v>
+      </c>
+      <c r="B45" s="27"/>
+      <c r="C45" s="44"/>
+      <c r="D45" s="44"/>
+      <c r="E45" s="38"/>
+      <c r="F45" s="28"/>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="41">
+        <v>14</v>
+      </c>
+      <c r="B46" s="27"/>
+      <c r="C46" s="44"/>
+      <c r="D46" s="44"/>
+      <c r="E46" s="38"/>
+      <c r="F46" s="28"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A3:H3"/>
+  </mergeCells>
+  <phoneticPr fontId="13" type="noConversion"/>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F19:F22 F8:F14" xr:uid="{D4C9D8DF-FB2B-4899-B3EC-249C311DB5C8}">
+      <formula1>"20,40,45,50"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.31496062992125984" right="0.31496062992125984" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A4916EE-2644-41CB-AAB9-F19957DCAC7B}">
+  <dimension ref="A1:J46"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3.140625" style="24" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.7109375" style="24" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" style="24" customWidth="1"/>
+    <col min="4" max="4" width="19.140625" style="24" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="24" customWidth="1"/>
+    <col min="6" max="6" width="14" style="24" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.140625" style="24" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="11.42578125" style="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="7"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="9">
+        <f>COUNTIF(C8:C14,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" s="8"/>
+    </row>
+    <row r="2" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="7"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="9">
+        <f>COUNTIFS(B19:B22,"&lt;&gt;",C19:C22,"VH")</f>
+        <v>0</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="9">
+        <f>COUNTA(C19:C28)-F2</f>
+        <v>0</v>
+      </c>
+      <c r="I2" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="J2" s="11">
+        <f>COUNTIF(H19:H24,"VIDE")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="79" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="79"/>
+      <c r="C3" s="79"/>
+      <c r="D3" s="79"/>
+      <c r="E3" s="79"/>
+      <c r="F3" s="79"/>
+      <c r="G3" s="79"/>
+      <c r="H3" s="79"/>
+      <c r="I3" s="8"/>
+      <c r="J3" s="8"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="7"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="8"/>
+    </row>
+    <row r="5" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="7"/>
+      <c r="B5" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="13">
+        <v>46264</v>
+      </c>
+      <c r="H5" s="8"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="8"/>
+    </row>
+    <row r="6" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="7"/>
+      <c r="B6" s="14"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8"/>
+      <c r="J6" s="8"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="42">
+        <v>2</v>
+      </c>
+      <c r="B8" s="73"/>
+      <c r="C8" s="74"/>
+      <c r="D8" s="75"/>
+      <c r="E8" s="75"/>
+      <c r="F8" s="76"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="41">
+        <v>3</v>
+      </c>
+      <c r="B9" s="77"/>
+      <c r="C9" s="74"/>
+      <c r="D9" s="78"/>
+      <c r="E9" s="76"/>
+      <c r="F9" s="76"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="8"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="42">
+        <v>4</v>
+      </c>
+      <c r="B10" s="77"/>
+      <c r="C10" s="74"/>
+      <c r="D10" s="76"/>
+      <c r="E10" s="76"/>
+      <c r="F10" s="76"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="42">
+        <v>5</v>
+      </c>
+      <c r="B11" s="51"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="50"/>
+      <c r="E11" s="50"/>
+      <c r="F11" s="50"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="41">
+        <v>6</v>
+      </c>
+      <c r="B12" s="51"/>
+      <c r="C12" s="27"/>
+      <c r="D12" s="50"/>
+      <c r="E12" s="50"/>
+      <c r="F12" s="50"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="41">
+        <v>7</v>
+      </c>
+      <c r="B13" s="51"/>
+      <c r="C13" s="27"/>
+      <c r="D13" s="44"/>
+      <c r="E13" s="44"/>
+      <c r="F13" s="41"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="8"/>
+      <c r="J13" s="8"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="42">
+        <v>8</v>
+      </c>
+      <c r="B14" s="41"/>
+      <c r="C14" s="27"/>
+      <c r="D14" s="44"/>
+      <c r="E14" s="44"/>
+      <c r="F14" s="41"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="8"/>
+    </row>
+    <row r="15" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="7"/>
+      <c r="B15" s="25"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="25"/>
+    </row>
+    <row r="16" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="7"/>
+      <c r="B16" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="G16" s="25"/>
+    </row>
+    <row r="17" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="7"/>
+      <c r="B17" s="14"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="8"/>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="B18" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="D18" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="E18" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="F18" s="17" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" s="41">
+        <v>1</v>
+      </c>
+      <c r="B19" s="72">
+        <v>46261</v>
+      </c>
+      <c r="C19" s="38"/>
+      <c r="D19" s="43"/>
+      <c r="E19" s="50"/>
+      <c r="F19" s="50"/>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" s="41">
+        <v>2</v>
+      </c>
+      <c r="B20" s="72"/>
+      <c r="C20" s="38"/>
+      <c r="D20" s="39"/>
+      <c r="E20" s="28"/>
+      <c r="F20" s="50"/>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" s="41">
+        <v>3</v>
+      </c>
+      <c r="B21" s="72"/>
+      <c r="C21" s="28"/>
+      <c r="D21" s="43"/>
+      <c r="E21" s="44"/>
+      <c r="F21" s="50"/>
+      <c r="G21" s="24" t="s">
+        <v>42</v>
+      </c>
+      <c r="J21" s="67"/>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" s="41">
+        <v>4</v>
+      </c>
+      <c r="B22" s="72"/>
+      <c r="C22" s="28"/>
+      <c r="D22" s="44"/>
+      <c r="E22" s="44"/>
+      <c r="F22" s="50"/>
+      <c r="J22" s="67"/>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" s="36">
+        <v>5</v>
+      </c>
+      <c r="B23" s="69"/>
+      <c r="D23" s="50"/>
+      <c r="E23" s="38"/>
+      <c r="F23" s="38"/>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" s="36">
+        <v>6</v>
+      </c>
+      <c r="B24" s="27"/>
+      <c r="C24" s="38"/>
+      <c r="D24" s="50"/>
+      <c r="E24" s="41"/>
+      <c r="F24" s="29"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" s="36">
+        <v>7</v>
+      </c>
+      <c r="B25" s="27"/>
+      <c r="C25" s="38"/>
+      <c r="D25" s="43"/>
+      <c r="E25" s="50"/>
+      <c r="F25" s="29"/>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" s="36">
+        <v>8</v>
+      </c>
+      <c r="B26" s="27"/>
+      <c r="C26" s="28"/>
+      <c r="D26" s="39"/>
+      <c r="E26" s="29"/>
+      <c r="F26" s="29"/>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" s="36">
+        <v>9</v>
+      </c>
+      <c r="B27" s="27"/>
+      <c r="C27" s="41"/>
+      <c r="D27" s="44"/>
+      <c r="E27" s="41"/>
+      <c r="F27" s="29"/>
+    </row>
+    <row r="28" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A28" s="36">
+        <v>10</v>
+      </c>
+      <c r="B28" s="27"/>
+      <c r="C28" s="41"/>
+      <c r="D28" s="44"/>
+      <c r="E28" s="41"/>
+      <c r="F28" s="29"/>
+      <c r="G28" s="25"/>
+    </row>
+    <row r="29" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A29" s="7"/>
+      <c r="B29" s="12"/>
+      <c r="C29" s="8"/>
+      <c r="D29" s="45"/>
+      <c r="E29" s="8"/>
+      <c r="F29" s="8"/>
+      <c r="G29" s="25"/>
+    </row>
+    <row r="30" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A30" s="7"/>
+      <c r="B30" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C30" s="8"/>
+      <c r="D30" s="45"/>
+      <c r="E30" s="8"/>
+      <c r="F30" s="8"/>
+      <c r="G30" s="25"/>
+    </row>
+    <row r="31" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="7"/>
+      <c r="B31" s="14"/>
+      <c r="C31" s="8"/>
+      <c r="D31" s="8"/>
+      <c r="E31" s="8"/>
+      <c r="F31" s="8"/>
+      <c r="G31" s="8"/>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="B32" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="C32" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="D32" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="E32" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="F32" s="17" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="41">
+        <v>1</v>
+      </c>
+      <c r="B33" s="72">
+        <v>46264</v>
+      </c>
+      <c r="C33" s="28" t="s">
+        <v>93</v>
+      </c>
+      <c r="D33" s="28" t="s">
+        <v>94</v>
+      </c>
+      <c r="E33" s="38">
+        <v>3578</v>
+      </c>
+      <c r="F33" s="28">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="41">
+        <v>2</v>
+      </c>
+      <c r="B34" s="72">
+        <v>46264</v>
+      </c>
+      <c r="C34" s="28" t="s">
+        <v>330</v>
+      </c>
+      <c r="D34" s="39">
+        <v>1072594</v>
+      </c>
+      <c r="E34" s="28">
+        <v>3573</v>
+      </c>
+      <c r="F34" s="28">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="41">
+        <v>3</v>
+      </c>
+      <c r="B35" s="72">
+        <v>46264</v>
+      </c>
+      <c r="C35" s="39" t="s">
+        <v>331</v>
+      </c>
+      <c r="D35" s="28">
+        <v>1072595</v>
+      </c>
+      <c r="E35" s="38">
+        <v>3574</v>
+      </c>
+      <c r="F35" s="28">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="41">
+        <v>4</v>
+      </c>
+      <c r="B36" s="27"/>
+      <c r="C36" s="40"/>
+      <c r="D36" s="40"/>
+      <c r="E36" s="40"/>
+      <c r="F36" s="28"/>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="41">
+        <v>5</v>
+      </c>
+      <c r="B37" s="27"/>
+      <c r="C37" s="40"/>
+      <c r="D37" s="40"/>
+      <c r="E37" s="40"/>
+      <c r="F37" s="28"/>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="41">
+        <v>6</v>
+      </c>
+      <c r="B38" s="27"/>
+      <c r="C38" s="44"/>
+      <c r="D38" s="44"/>
+      <c r="E38" s="38"/>
+      <c r="F38" s="28"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="41">
+        <v>7</v>
+      </c>
+      <c r="B39" s="27"/>
+      <c r="C39" s="44"/>
+      <c r="D39" s="44"/>
+      <c r="E39" s="38"/>
+      <c r="F39" s="28"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="41">
+        <v>8</v>
+      </c>
+      <c r="B40" s="27"/>
+      <c r="C40" s="44"/>
+      <c r="D40" s="44"/>
+      <c r="E40" s="38"/>
+      <c r="F40" s="28"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="41">
+        <v>9</v>
+      </c>
+      <c r="B41" s="27"/>
+      <c r="C41" s="44"/>
+      <c r="D41" s="44"/>
+      <c r="E41" s="38"/>
+      <c r="F41" s="28"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="41">
+        <v>10</v>
+      </c>
+      <c r="B42" s="27"/>
+      <c r="C42" s="44"/>
+      <c r="D42" s="44"/>
+      <c r="E42" s="38"/>
+      <c r="F42" s="28"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="41">
+        <v>11</v>
+      </c>
+      <c r="B43" s="27"/>
+      <c r="C43" s="44"/>
+      <c r="D43" s="44"/>
+      <c r="E43" s="38"/>
+      <c r="F43" s="28"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="41">
+        <v>12</v>
+      </c>
+      <c r="B44" s="27"/>
+      <c r="C44" s="44"/>
+      <c r="D44" s="44"/>
+      <c r="E44" s="38"/>
+      <c r="F44" s="28"/>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="41">
+        <v>13</v>
+      </c>
+      <c r="B45" s="27"/>
+      <c r="C45" s="44"/>
+      <c r="D45" s="44"/>
+      <c r="E45" s="38"/>
+      <c r="F45" s="28"/>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="41">
+        <v>14</v>
+      </c>
+      <c r="B46" s="27"/>
+      <c r="C46" s="44"/>
+      <c r="D46" s="44"/>
+      <c r="E46" s="38"/>
+      <c r="F46" s="28"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A3:H3"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F19:F22 F8:F14" xr:uid="{1F91CDEA-9C92-4B27-B4C3-CC08439F0E37}">
+      <formula1>"20,40,45,50"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.31496062992125984" right="0.31496062992125984" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1557275D-72DC-4D7D-8158-6CE5C8EF6E1C}">
+  <dimension ref="A1:J46"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3.140625" style="24" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.7109375" style="24" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" style="24" customWidth="1"/>
+    <col min="4" max="4" width="19.140625" style="24" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="24" customWidth="1"/>
+    <col min="6" max="6" width="14" style="24" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.140625" style="24" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="11.42578125" style="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="7"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="9">
+        <f>COUNTIF(C8:C14,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" s="8"/>
+    </row>
+    <row r="2" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="7"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="9">
+        <f>COUNTIFS(B19:B22,"&lt;&gt;",C19:C22,"VH")</f>
+        <v>0</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="9">
+        <f>COUNTA(C19:C28)-F2</f>
+        <v>0</v>
+      </c>
+      <c r="I2" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="J2" s="11">
+        <f>COUNTIF(H19:H24,"VIDE")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="79" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="79"/>
+      <c r="C3" s="79"/>
+      <c r="D3" s="79"/>
+      <c r="E3" s="79"/>
+      <c r="F3" s="79"/>
+      <c r="G3" s="79"/>
+      <c r="H3" s="79"/>
+      <c r="I3" s="8"/>
+      <c r="J3" s="8"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="7"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="8"/>
+    </row>
+    <row r="5" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="7"/>
+      <c r="B5" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="13">
+        <v>46265</v>
+      </c>
+      <c r="H5" s="8"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="8"/>
+    </row>
+    <row r="6" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="7"/>
+      <c r="B6" s="14"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8"/>
+      <c r="J6" s="8"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="42">
+        <v>2</v>
+      </c>
+      <c r="B8" s="73"/>
+      <c r="C8" s="74"/>
+      <c r="D8" s="75"/>
+      <c r="E8" s="75"/>
+      <c r="F8" s="76"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="41">
+        <v>3</v>
+      </c>
+      <c r="B9" s="77"/>
+      <c r="C9" s="74"/>
+      <c r="D9" s="78"/>
+      <c r="E9" s="76"/>
+      <c r="F9" s="76"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="8"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="42">
+        <v>4</v>
+      </c>
+      <c r="B10" s="77"/>
+      <c r="C10" s="74"/>
+      <c r="D10" s="76"/>
+      <c r="E10" s="76"/>
+      <c r="F10" s="76"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="42">
+        <v>5</v>
+      </c>
+      <c r="B11" s="51"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="50"/>
+      <c r="E11" s="50"/>
+      <c r="F11" s="50"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="41">
+        <v>6</v>
+      </c>
+      <c r="B12" s="51"/>
+      <c r="C12" s="27"/>
+      <c r="D12" s="50"/>
+      <c r="E12" s="50"/>
+      <c r="F12" s="50"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="41">
+        <v>7</v>
+      </c>
+      <c r="B13" s="51"/>
+      <c r="C13" s="27"/>
+      <c r="D13" s="44"/>
+      <c r="E13" s="44"/>
+      <c r="F13" s="41"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="8"/>
+      <c r="J13" s="8"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="42">
+        <v>8</v>
+      </c>
+      <c r="B14" s="41"/>
+      <c r="C14" s="27"/>
+      <c r="D14" s="44"/>
+      <c r="E14" s="44"/>
+      <c r="F14" s="41"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="8"/>
+    </row>
+    <row r="15" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="7"/>
+      <c r="B15" s="25"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="25"/>
+    </row>
+    <row r="16" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="7"/>
+      <c r="B16" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="G16" s="25"/>
+    </row>
+    <row r="17" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="7"/>
+      <c r="B17" s="14"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="8"/>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="B18" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="D18" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="E18" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="F18" s="17" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" s="41">
+        <v>1</v>
+      </c>
+      <c r="B19" s="72">
+        <v>46261</v>
+      </c>
+      <c r="C19" s="38"/>
+      <c r="D19" s="43"/>
+      <c r="E19" s="50"/>
+      <c r="F19" s="50"/>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" s="41">
+        <v>2</v>
+      </c>
+      <c r="B20" s="72"/>
+      <c r="C20" s="38"/>
+      <c r="D20" s="39"/>
+      <c r="E20" s="28"/>
+      <c r="F20" s="50"/>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" s="41">
+        <v>3</v>
+      </c>
+      <c r="B21" s="72"/>
+      <c r="C21" s="28"/>
+      <c r="D21" s="43"/>
+      <c r="E21" s="44"/>
+      <c r="F21" s="50"/>
+      <c r="G21" s="24" t="s">
+        <v>42</v>
+      </c>
+      <c r="J21" s="67"/>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" s="41">
+        <v>4</v>
+      </c>
+      <c r="B22" s="72"/>
+      <c r="C22" s="28"/>
+      <c r="D22" s="44"/>
+      <c r="E22" s="44"/>
+      <c r="F22" s="50"/>
+      <c r="J22" s="67"/>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" s="36">
+        <v>5</v>
+      </c>
+      <c r="B23" s="69"/>
+      <c r="D23" s="50"/>
+      <c r="E23" s="38"/>
+      <c r="F23" s="38"/>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" s="36">
+        <v>6</v>
+      </c>
+      <c r="B24" s="27"/>
+      <c r="C24" s="38"/>
+      <c r="D24" s="50"/>
+      <c r="E24" s="41"/>
+      <c r="F24" s="29"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" s="36">
+        <v>7</v>
+      </c>
+      <c r="B25" s="27"/>
+      <c r="C25" s="38"/>
+      <c r="D25" s="43"/>
+      <c r="E25" s="50"/>
+      <c r="F25" s="29"/>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" s="36">
+        <v>8</v>
+      </c>
+      <c r="B26" s="27"/>
+      <c r="C26" s="28"/>
+      <c r="D26" s="39"/>
+      <c r="E26" s="29"/>
+      <c r="F26" s="29"/>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" s="36">
+        <v>9</v>
+      </c>
+      <c r="B27" s="27"/>
+      <c r="C27" s="41"/>
+      <c r="D27" s="44"/>
+      <c r="E27" s="41"/>
+      <c r="F27" s="29"/>
+    </row>
+    <row r="28" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A28" s="36">
+        <v>10</v>
+      </c>
+      <c r="B28" s="27"/>
+      <c r="C28" s="41"/>
+      <c r="D28" s="44"/>
+      <c r="E28" s="41"/>
+      <c r="F28" s="29"/>
+      <c r="G28" s="25"/>
+    </row>
+    <row r="29" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A29" s="7"/>
+      <c r="B29" s="12"/>
+      <c r="C29" s="8"/>
+      <c r="D29" s="45"/>
+      <c r="E29" s="8"/>
+      <c r="F29" s="8"/>
+      <c r="G29" s="25"/>
+    </row>
+    <row r="30" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A30" s="7"/>
+      <c r="B30" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C30" s="8"/>
+      <c r="D30" s="45"/>
+      <c r="E30" s="8"/>
+      <c r="F30" s="8"/>
+      <c r="G30" s="25"/>
+    </row>
+    <row r="31" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="7"/>
+      <c r="B31" s="14"/>
+      <c r="C31" s="8"/>
+      <c r="D31" s="8"/>
+      <c r="E31" s="8"/>
+      <c r="F31" s="8"/>
+      <c r="G31" s="8"/>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="B32" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="C32" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="D32" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="E32" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="F32" s="17" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="41">
+        <v>1</v>
+      </c>
+      <c r="B33" s="72">
+        <v>46264</v>
+      </c>
+      <c r="C33" s="28"/>
+      <c r="D33" s="28"/>
+      <c r="E33" s="38"/>
+      <c r="F33" s="28"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="41">
+        <v>2</v>
+      </c>
+      <c r="B34" s="72">
+        <v>46264</v>
+      </c>
+      <c r="C34" s="28"/>
+      <c r="D34" s="39"/>
+      <c r="E34" s="28"/>
+      <c r="F34" s="28"/>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="41">
+        <v>3</v>
+      </c>
+      <c r="B35" s="72">
+        <v>46264</v>
+      </c>
+      <c r="C35" s="39"/>
+      <c r="D35" s="28"/>
+      <c r="E35" s="38"/>
+      <c r="F35" s="28"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="41">
+        <v>4</v>
+      </c>
+      <c r="B36" s="27"/>
+      <c r="C36" s="40"/>
+      <c r="D36" s="40"/>
+      <c r="E36" s="40"/>
+      <c r="F36" s="28"/>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="41">
+        <v>5</v>
+      </c>
+      <c r="B37" s="27"/>
+      <c r="C37" s="40"/>
+      <c r="D37" s="40"/>
+      <c r="E37" s="40"/>
+      <c r="F37" s="28"/>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="41">
+        <v>6</v>
+      </c>
+      <c r="B38" s="27"/>
+      <c r="C38" s="44"/>
+      <c r="D38" s="44"/>
+      <c r="E38" s="38"/>
+      <c r="F38" s="28"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="41">
+        <v>7</v>
+      </c>
+      <c r="B39" s="27"/>
+      <c r="C39" s="44"/>
+      <c r="D39" s="44"/>
+      <c r="E39" s="38"/>
+      <c r="F39" s="28"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="41">
+        <v>8</v>
+      </c>
+      <c r="B40" s="27"/>
+      <c r="C40" s="44"/>
+      <c r="D40" s="44"/>
+      <c r="E40" s="38"/>
+      <c r="F40" s="28"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="41">
+        <v>9</v>
+      </c>
+      <c r="B41" s="27"/>
+      <c r="C41" s="44"/>
+      <c r="D41" s="44"/>
+      <c r="E41" s="38"/>
+      <c r="F41" s="28"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="41">
+        <v>10</v>
+      </c>
+      <c r="B42" s="27"/>
+      <c r="C42" s="44"/>
+      <c r="D42" s="44"/>
+      <c r="E42" s="38"/>
+      <c r="F42" s="28"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="41">
+        <v>11</v>
+      </c>
+      <c r="B43" s="27"/>
+      <c r="C43" s="44"/>
+      <c r="D43" s="44"/>
+      <c r="E43" s="38"/>
+      <c r="F43" s="28"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="41">
+        <v>12</v>
+      </c>
+      <c r="B44" s="27"/>
+      <c r="C44" s="44"/>
+      <c r="D44" s="44"/>
+      <c r="E44" s="38"/>
+      <c r="F44" s="28"/>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="41">
+        <v>13</v>
+      </c>
+      <c r="B45" s="27"/>
+      <c r="C45" s="44"/>
+      <c r="D45" s="44"/>
+      <c r="E45" s="38"/>
+      <c r="F45" s="28"/>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="41">
+        <v>14</v>
+      </c>
+      <c r="B46" s="27"/>
+      <c r="C46" s="44"/>
+      <c r="D46" s="44"/>
+      <c r="E46" s="38"/>
+      <c r="F46" s="28"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A3:H3"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F19:F22 F8:F14" xr:uid="{38802EAB-7B00-4ED4-9E9A-7DDF9927DDF7}">
+      <formula1>"20,40,45,50"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -9967,16 +12061,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="8" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="70" t="s">
+      <c r="A3" s="79" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="70"/>
-      <c r="C3" s="70"/>
-      <c r="D3" s="70"/>
-      <c r="E3" s="70"/>
-      <c r="F3" s="70"/>
-      <c r="G3" s="70"/>
-      <c r="H3" s="70"/>
+      <c r="B3" s="79"/>
+      <c r="C3" s="79"/>
+      <c r="D3" s="79"/>
+      <c r="E3" s="79"/>
+      <c r="F3" s="79"/>
+      <c r="G3" s="79"/>
+      <c r="H3" s="79"/>
     </row>
     <row r="4" spans="1:10" s="8" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="7"/>
@@ -10579,16 +12673,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="8" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="70" t="s">
+      <c r="A3" s="79" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="70"/>
-      <c r="C3" s="70"/>
-      <c r="D3" s="70"/>
-      <c r="E3" s="70"/>
-      <c r="F3" s="70"/>
-      <c r="G3" s="70"/>
-      <c r="H3" s="70"/>
+      <c r="B3" s="79"/>
+      <c r="C3" s="79"/>
+      <c r="D3" s="79"/>
+      <c r="E3" s="79"/>
+      <c r="F3" s="79"/>
+      <c r="G3" s="79"/>
+      <c r="H3" s="79"/>
     </row>
     <row r="4" spans="1:10" s="8" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="7"/>
@@ -11058,16 +13152,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="8" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="70" t="s">
+      <c r="A3" s="79" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="70"/>
-      <c r="C3" s="70"/>
-      <c r="D3" s="70"/>
-      <c r="E3" s="70"/>
-      <c r="F3" s="70"/>
-      <c r="G3" s="70"/>
-      <c r="H3" s="70"/>
+      <c r="B3" s="79"/>
+      <c r="C3" s="79"/>
+      <c r="D3" s="79"/>
+      <c r="E3" s="79"/>
+      <c r="F3" s="79"/>
+      <c r="G3" s="79"/>
+      <c r="H3" s="79"/>
     </row>
     <row r="4" spans="1:10" s="8" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="7"/>
@@ -11129,7 +13223,7 @@
       <c r="A9" s="42">
         <v>2</v>
       </c>
-      <c r="B9" s="72" t="s">
+      <c r="B9" s="80" t="s">
         <v>142</v>
       </c>
       <c r="C9" s="51">
@@ -11149,7 +13243,7 @@
       <c r="A10" s="36">
         <v>3</v>
       </c>
-      <c r="B10" s="73"/>
+      <c r="B10" s="81"/>
       <c r="C10" s="51">
         <v>46239</v>
       </c>
@@ -11167,7 +13261,7 @@
       <c r="A11" s="42">
         <v>4</v>
       </c>
-      <c r="B11" s="73"/>
+      <c r="B11" s="81"/>
       <c r="C11" s="51">
         <v>46239</v>
       </c>
@@ -11185,7 +13279,7 @@
       <c r="A12" s="42">
         <v>5</v>
       </c>
-      <c r="B12" s="73"/>
+      <c r="B12" s="81"/>
       <c r="C12" s="51">
         <v>46239</v>
       </c>
@@ -11203,7 +13297,7 @@
       <c r="A13" s="36">
         <v>6</v>
       </c>
-      <c r="B13" s="73"/>
+      <c r="B13" s="81"/>
       <c r="C13" s="51"/>
       <c r="D13" s="54"/>
       <c r="E13" s="53"/>
@@ -11213,7 +13307,7 @@
       <c r="A14" s="42">
         <v>7</v>
       </c>
-      <c r="B14" s="73"/>
+      <c r="B14" s="81"/>
       <c r="C14" s="51">
         <v>46239</v>
       </c>
@@ -11231,7 +13325,7 @@
       <c r="A15" s="42">
         <v>8</v>
       </c>
-      <c r="B15" s="74"/>
+      <c r="B15" s="82"/>
       <c r="C15" s="51">
         <v>46239</v>
       </c>
@@ -11249,7 +13343,7 @@
       <c r="A16" s="36">
         <v>9</v>
       </c>
-      <c r="B16" s="72" t="s">
+      <c r="B16" s="80" t="s">
         <v>143</v>
       </c>
       <c r="C16" s="51">
@@ -11269,7 +13363,7 @@
       <c r="A17" s="42">
         <v>10</v>
       </c>
-      <c r="B17" s="74"/>
+      <c r="B17" s="82"/>
       <c r="C17" s="51">
         <v>46239</v>
       </c>
@@ -11287,10 +13381,10 @@
       <c r="A18" s="42">
         <v>16</v>
       </c>
-      <c r="B18" s="72" t="s">
+      <c r="B18" s="80" t="s">
         <v>145</v>
       </c>
-      <c r="C18" s="77"/>
+      <c r="C18" s="85"/>
       <c r="D18" s="52" t="s">
         <v>117</v>
       </c>
@@ -11300,7 +13394,7 @@
       <c r="F18" s="54" t="s">
         <v>95</v>
       </c>
-      <c r="G18" s="79" t="s">
+      <c r="G18" s="87" t="s">
         <v>154</v>
       </c>
     </row>
@@ -11308,8 +13402,8 @@
       <c r="A19" s="42">
         <v>17</v>
       </c>
-      <c r="B19" s="74"/>
-      <c r="C19" s="78"/>
+      <c r="B19" s="82"/>
+      <c r="C19" s="86"/>
       <c r="D19" s="52" t="s">
         <v>119</v>
       </c>
@@ -11319,13 +13413,13 @@
       <c r="F19" s="54" t="s">
         <v>95</v>
       </c>
-      <c r="G19" s="79"/>
+      <c r="G19" s="87"/>
     </row>
     <row r="20" spans="1:7" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="36">
         <v>18</v>
       </c>
-      <c r="B20" s="72" t="s">
+      <c r="B20" s="80" t="s">
         <v>146</v>
       </c>
       <c r="C20" s="51">
@@ -11345,7 +13439,7 @@
       <c r="A21" s="42">
         <v>19</v>
       </c>
-      <c r="B21" s="74"/>
+      <c r="B21" s="82"/>
       <c r="C21" s="51">
         <v>46239</v>
       </c>
@@ -11363,7 +13457,7 @@
       <c r="A22" s="42">
         <v>20</v>
       </c>
-      <c r="B22" s="72" t="s">
+      <c r="B22" s="80" t="s">
         <v>147</v>
       </c>
       <c r="C22" s="51">
@@ -11383,7 +13477,7 @@
       <c r="A23" s="36">
         <v>21</v>
       </c>
-      <c r="B23" s="73"/>
+      <c r="B23" s="81"/>
       <c r="C23" s="51"/>
       <c r="D23" s="52" t="s">
         <v>127</v>
@@ -11399,7 +13493,7 @@
       <c r="A24" s="42">
         <v>22</v>
       </c>
-      <c r="B24" s="74"/>
+      <c r="B24" s="82"/>
       <c r="C24" s="51">
         <v>46239</v>
       </c>
@@ -11417,7 +13511,7 @@
       <c r="A25" s="42">
         <v>23</v>
       </c>
-      <c r="B25" s="75" t="s">
+      <c r="B25" s="83" t="s">
         <v>148</v>
       </c>
       <c r="C25" s="51"/>
@@ -11435,7 +13529,7 @@
       <c r="A26" s="36">
         <v>24</v>
       </c>
-      <c r="B26" s="75"/>
+      <c r="B26" s="83"/>
       <c r="C26" s="51">
         <v>46239</v>
       </c>
@@ -11453,7 +13547,7 @@
       <c r="A27" s="42">
         <v>25</v>
       </c>
-      <c r="B27" s="76"/>
+      <c r="B27" s="84"/>
       <c r="C27" s="51">
         <v>46239</v>
       </c>
@@ -11471,7 +13565,7 @@
       <c r="A28" s="42">
         <v>26</v>
       </c>
-      <c r="B28" s="75" t="s">
+      <c r="B28" s="83" t="s">
         <v>149</v>
       </c>
       <c r="C28" s="51">
@@ -11491,7 +13585,7 @@
       <c r="A29" s="36">
         <v>27</v>
       </c>
-      <c r="B29" s="76"/>
+      <c r="B29" s="84"/>
       <c r="C29" s="51">
         <v>46239</v>
       </c>
@@ -11754,16 +13848,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="8" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="70" t="s">
+      <c r="A3" s="79" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="70"/>
-      <c r="C3" s="70"/>
-      <c r="D3" s="70"/>
-      <c r="E3" s="70"/>
-      <c r="F3" s="70"/>
-      <c r="G3" s="70"/>
-      <c r="H3" s="70"/>
+      <c r="B3" s="79"/>
+      <c r="C3" s="79"/>
+      <c r="D3" s="79"/>
+      <c r="E3" s="79"/>
+      <c r="F3" s="79"/>
+      <c r="G3" s="79"/>
+      <c r="H3" s="79"/>
     </row>
     <row r="4" spans="1:10" s="8" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="7"/>
@@ -11825,7 +13919,7 @@
       <c r="A9" s="42">
         <v>2</v>
       </c>
-      <c r="B9" s="77" t="s">
+      <c r="B9" s="85" t="s">
         <v>144</v>
       </c>
       <c r="C9" s="27">
@@ -11845,7 +13939,7 @@
       <c r="A10" s="36">
         <v>3</v>
       </c>
-      <c r="B10" s="80"/>
+      <c r="B10" s="88"/>
       <c r="C10" s="27">
         <v>46240</v>
       </c>
@@ -11863,7 +13957,7 @@
       <c r="A11" s="42">
         <v>4</v>
       </c>
-      <c r="B11" s="80"/>
+      <c r="B11" s="88"/>
       <c r="C11" s="27"/>
       <c r="D11" s="41" t="s">
         <v>112</v>
@@ -11879,7 +13973,7 @@
       <c r="A12" s="42">
         <v>5</v>
       </c>
-      <c r="B12" s="80"/>
+      <c r="B12" s="88"/>
       <c r="C12" s="27"/>
       <c r="D12" s="41" t="s">
         <v>114</v>
@@ -11895,7 +13989,7 @@
       <c r="A13" s="36">
         <v>6</v>
       </c>
-      <c r="B13" s="78"/>
+      <c r="B13" s="86"/>
       <c r="C13" s="27">
         <v>46240</v>
       </c>
@@ -12432,16 +14526,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="8" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="70" t="s">
+      <c r="A3" s="79" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="70"/>
-      <c r="C3" s="70"/>
-      <c r="D3" s="70"/>
-      <c r="E3" s="70"/>
-      <c r="F3" s="70"/>
-      <c r="G3" s="70"/>
-      <c r="H3" s="70"/>
+      <c r="B3" s="79"/>
+      <c r="C3" s="79"/>
+      <c r="D3" s="79"/>
+      <c r="E3" s="79"/>
+      <c r="F3" s="79"/>
+      <c r="G3" s="79"/>
+      <c r="H3" s="79"/>
     </row>
     <row r="4" spans="1:10" s="8" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="7"/>
@@ -12483,7 +14577,7 @@
       <c r="A8" s="36">
         <v>1</v>
       </c>
-      <c r="B8" s="77" t="s">
+      <c r="B8" s="85" t="s">
         <v>144</v>
       </c>
       <c r="C8" s="27">
@@ -12503,7 +14597,7 @@
       <c r="A9" s="42">
         <v>2</v>
       </c>
-      <c r="B9" s="78"/>
+      <c r="B9" s="86"/>
       <c r="C9" s="27">
         <v>46243</v>
       </c>
@@ -12945,16 +15039,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="8" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="70" t="s">
+      <c r="A3" s="79" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="70"/>
-      <c r="C3" s="70"/>
-      <c r="D3" s="70"/>
-      <c r="E3" s="70"/>
-      <c r="F3" s="70"/>
-      <c r="G3" s="70"/>
-      <c r="H3" s="70"/>
+      <c r="B3" s="79"/>
+      <c r="C3" s="79"/>
+      <c r="D3" s="79"/>
+      <c r="E3" s="79"/>
+      <c r="F3" s="79"/>
+      <c r="G3" s="79"/>
+      <c r="H3" s="79"/>
     </row>
     <row r="4" spans="1:10" s="8" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="7"/>
@@ -12996,7 +15090,7 @@
       <c r="A8" s="36">
         <v>1</v>
       </c>
-      <c r="B8" s="81" t="s">
+      <c r="B8" s="89" t="s">
         <v>194</v>
       </c>
       <c r="C8" s="27">
@@ -13016,7 +15110,7 @@
       <c r="A9" s="42">
         <v>2</v>
       </c>
-      <c r="B9" s="81"/>
+      <c r="B9" s="89"/>
       <c r="C9" s="27"/>
       <c r="D9" s="29">
         <v>3517</v>
@@ -13032,7 +15126,7 @@
       <c r="A10" s="36">
         <v>3</v>
       </c>
-      <c r="B10" s="81"/>
+      <c r="B10" s="89"/>
       <c r="C10" s="27">
         <v>46244</v>
       </c>
@@ -13050,7 +15144,7 @@
       <c r="A11" s="42">
         <v>4</v>
       </c>
-      <c r="B11" s="81"/>
+      <c r="B11" s="89"/>
       <c r="C11" s="27">
         <v>46244</v>
       </c>
@@ -13688,16 +15782,16 @@
       </c>
     </row>
     <row r="3" spans="1:11" s="8" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="70" t="s">
+      <c r="A3" s="79" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="70"/>
-      <c r="C3" s="70"/>
-      <c r="D3" s="70"/>
-      <c r="E3" s="70"/>
-      <c r="F3" s="70"/>
-      <c r="G3" s="70"/>
-      <c r="H3" s="70"/>
+      <c r="B3" s="79"/>
+      <c r="C3" s="79"/>
+      <c r="D3" s="79"/>
+      <c r="E3" s="79"/>
+      <c r="F3" s="79"/>
+      <c r="G3" s="79"/>
+      <c r="H3" s="79"/>
     </row>
     <row r="4" spans="1:11" s="8" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="7"/>
@@ -13757,7 +15851,7 @@
       <c r="F8" s="50" t="s">
         <v>86</v>
       </c>
-      <c r="G8" s="85"/>
+      <c r="G8" s="71"/>
     </row>
     <row r="9" spans="1:11" s="8" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="41">
@@ -13778,7 +15872,7 @@
       <c r="F9" s="50" t="s">
         <v>220</v>
       </c>
-      <c r="G9" s="85">
+      <c r="G9" s="71">
         <v>46254</v>
       </c>
     </row>
@@ -13801,7 +15895,7 @@
       <c r="F10" s="50" t="s">
         <v>220</v>
       </c>
-      <c r="G10" s="85">
+      <c r="G10" s="71">
         <v>46254</v>
       </c>
     </row>
